--- a/周度_工厂配送兔司家门店货品对比表及销售排行表_格式化模板.xlsx
+++ b/周度_工厂配送兔司家门店货品对比表及销售排行表_格式化模板.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wadec\Documents\projects\mainyan-auto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D85925F7-DF15-4D3E-952E-E45AECB504FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60A3F250-4E1E-45D9-B8E0-1BA0CC493D15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="15552" windowHeight="16656" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="配送门店业绩表 5.25-5.31" sheetId="4" r:id="rId1"/>
@@ -1163,7 +1163,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1257,21 +1257,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1287,30 +1272,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="9" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1323,11 +1284,53 @@
     <xf numFmtId="176" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1839,23 +1842,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="22" customFormat="1" ht="36" customHeight="1">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="31" t="s">
         <v>268</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="38"/>
-      <c r="K1" s="38"/>
-      <c r="L1" s="36"/>
-      <c r="M1" s="36"/>
-      <c r="N1" s="36"/>
-      <c r="O1" s="36"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="N1" s="31"/>
+      <c r="O1" s="31"/>
       <c r="P1" s="21"/>
       <c r="Q1" s="21"/>
     </row>
@@ -1907,57 +1910,57 @@
       </c>
     </row>
     <row r="3" spans="1:17" ht="22.05" customHeight="1">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="40"/>
-      <c r="C3" s="32">
+      <c r="B3" s="35"/>
+      <c r="C3" s="47">
         <f>SUM(C4:C5)</f>
         <v>7226.4400000000005</v>
       </c>
-      <c r="D3" s="32">
+      <c r="D3" s="47">
         <f>SUM(D4:D5)</f>
         <v>7046.4400000000005</v>
       </c>
-      <c r="E3" s="33">
+      <c r="E3" s="48">
         <f>SUM(E4:E5)</f>
         <v>2</v>
       </c>
-      <c r="F3" s="33">
+      <c r="F3" s="48">
         <f>SUM(F4:F5)</f>
         <v>180</v>
       </c>
-      <c r="G3" s="41">
+      <c r="G3" s="49">
         <v>9781</v>
       </c>
-      <c r="H3" s="41">
+      <c r="H3" s="49">
         <v>16508.3</v>
       </c>
-      <c r="I3" s="35">
+      <c r="I3" s="50">
         <f t="shared" ref="I3:O3" si="0">SUM(I4:I5)</f>
         <v>2</v>
       </c>
-      <c r="J3" s="35">
+      <c r="J3" s="50">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K3" s="35">
+      <c r="K3" s="50">
         <f t="shared" si="0"/>
         <v>672</v>
       </c>
-      <c r="L3" s="35">
+      <c r="L3" s="50">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M3" s="35">
+      <c r="M3" s="50">
         <f t="shared" si="0"/>
         <v>672</v>
       </c>
-      <c r="N3" s="35">
+      <c r="N3" s="50">
         <f t="shared" si="0"/>
         <v>7226.4400000000005</v>
       </c>
-      <c r="O3" s="35">
+      <c r="O3" s="50">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -1970,36 +1973,36 @@
       <c r="B4" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="31">
+      <c r="C4" s="51">
         <v>5912.14</v>
       </c>
-      <c r="D4" s="32">
+      <c r="D4" s="47">
         <f>C4-F4</f>
         <v>5812.14</v>
       </c>
-      <c r="E4" s="33">
-        <v>1</v>
-      </c>
-      <c r="F4" s="33">
+      <c r="E4" s="48">
+        <v>1</v>
+      </c>
+      <c r="F4" s="48">
         <v>100</v>
       </c>
-      <c r="G4" s="42"/>
-      <c r="H4" s="42"/>
-      <c r="I4" s="28">
-        <v>1</v>
-      </c>
-      <c r="J4" s="28"/>
-      <c r="K4" s="28">
+      <c r="G4" s="52"/>
+      <c r="H4" s="52"/>
+      <c r="I4" s="53">
+        <v>1</v>
+      </c>
+      <c r="J4" s="53"/>
+      <c r="K4" s="53">
         <v>604</v>
       </c>
-      <c r="L4" s="28"/>
-      <c r="M4" s="28">
+      <c r="L4" s="53"/>
+      <c r="M4" s="53">
         <v>604</v>
       </c>
-      <c r="N4" s="34">
+      <c r="N4" s="54">
         <v>5912.14</v>
       </c>
-      <c r="O4" s="28"/>
+      <c r="O4" s="53"/>
     </row>
     <row r="5" spans="1:17" ht="22.05" customHeight="1">
       <c r="A5" s="28">
@@ -2009,36 +2012,36 @@
       <c r="B5" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="31">
+      <c r="C5" s="51">
         <v>1314.3</v>
       </c>
-      <c r="D5" s="32">
+      <c r="D5" s="47">
         <f t="shared" ref="D5" si="2">C5-F5</f>
         <v>1234.3</v>
       </c>
-      <c r="E5" s="33">
-        <v>1</v>
-      </c>
-      <c r="F5" s="33">
+      <c r="E5" s="48">
+        <v>1</v>
+      </c>
+      <c r="F5" s="48">
         <v>80</v>
       </c>
-      <c r="G5" s="43"/>
-      <c r="H5" s="43"/>
-      <c r="I5" s="28">
-        <v>1</v>
-      </c>
-      <c r="J5" s="28"/>
-      <c r="K5" s="28">
+      <c r="G5" s="55"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="53">
+        <v>1</v>
+      </c>
+      <c r="J5" s="53"/>
+      <c r="K5" s="53">
         <v>68</v>
       </c>
-      <c r="L5" s="28"/>
-      <c r="M5" s="28">
+      <c r="L5" s="53"/>
+      <c r="M5" s="53">
         <v>68</v>
       </c>
-      <c r="N5" s="34">
+      <c r="N5" s="54">
         <v>1314.3</v>
       </c>
-      <c r="O5" s="28"/>
+      <c r="O5" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2088,104 +2091,104 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" s="10" customFormat="1" ht="25.05" customHeight="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="50"/>
-      <c r="M1" s="49"/>
-      <c r="N1" s="50"/>
-      <c r="O1" s="49"/>
-      <c r="P1" s="50"/>
-      <c r="Q1" s="49"/>
-      <c r="R1" s="50"/>
-      <c r="S1" s="49"/>
-      <c r="T1" s="50"/>
-      <c r="U1" s="49"/>
-      <c r="V1" s="50"/>
-      <c r="W1" s="49"/>
-      <c r="X1" s="50"/>
-      <c r="Y1" s="49"/>
-      <c r="Z1" s="50"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="36"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="36"/>
+      <c r="P1" s="37"/>
+      <c r="Q1" s="36"/>
+      <c r="R1" s="37"/>
+      <c r="S1" s="36"/>
+      <c r="T1" s="37"/>
+      <c r="U1" s="36"/>
+      <c r="V1" s="37"/>
+      <c r="W1" s="36"/>
+      <c r="X1" s="37"/>
+      <c r="Y1" s="36"/>
+      <c r="Z1" s="37"/>
       <c r="AA1" s="11"/>
       <c r="AB1" s="12"/>
     </row>
     <row r="2" spans="1:28" ht="19.95" customHeight="1">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="47" t="s">
+      <c r="C2" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="47" t="s">
+      <c r="D2" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="47" t="s">
+      <c r="E2" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="47" t="s">
+      <c r="F2" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="51" t="s">
+      <c r="G2" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="52"/>
-      <c r="I2" s="46" t="s">
+      <c r="H2" s="39"/>
+      <c r="I2" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="53"/>
-      <c r="K2" s="46" t="s">
+      <c r="J2" s="41"/>
+      <c r="K2" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="L2" s="53"/>
-      <c r="M2" s="44" t="s">
+      <c r="L2" s="41"/>
+      <c r="M2" s="42" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="54"/>
-      <c r="O2" s="44" t="s">
+      <c r="N2" s="43"/>
+      <c r="O2" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="P2" s="54"/>
-      <c r="Q2" s="44" t="s">
+      <c r="P2" s="43"/>
+      <c r="Q2" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="R2" s="54"/>
-      <c r="S2" s="44" t="s">
+      <c r="R2" s="43"/>
+      <c r="S2" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="T2" s="54"/>
-      <c r="U2" s="44" t="s">
+      <c r="T2" s="43"/>
+      <c r="U2" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="V2" s="54"/>
-      <c r="W2" s="44" t="s">
+      <c r="V2" s="43"/>
+      <c r="W2" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="X2" s="54"/>
-      <c r="Y2" s="46" t="s">
+      <c r="X2" s="43"/>
+      <c r="Y2" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="Z2" s="53"/>
+      <c r="Z2" s="41"/>
     </row>
     <row r="3" spans="1:28" ht="19.95" customHeight="1">
-      <c r="A3" s="45"/>
-      <c r="B3" s="46"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
+      <c r="A3" s="44"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
       <c r="G3" s="6" t="s">
         <v>27</v>
       </c>
@@ -2248,14 +2251,14 @@
       </c>
     </row>
     <row r="4" spans="1:28" ht="19.95" customHeight="1">
-      <c r="A4" s="44" t="s">
+      <c r="A4" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="44"/>
-      <c r="C4" s="44"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="44"/>
+      <c r="B4" s="42"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="42"/>
+      <c r="F4" s="42"/>
       <c r="G4" s="6">
         <f t="shared" ref="G4:L4" si="0">SUM(G5:G110)</f>
         <v>3063</v>
@@ -7905,6 +7908,13 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
     <mergeCell ref="A1:Z1"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="I2:J2"/>
@@ -7916,13 +7926,6 @@
     <mergeCell ref="U2:V2"/>
     <mergeCell ref="W2:X2"/>
     <mergeCell ref="Y2:Z2"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7946,16 +7949,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="36" t="s">
         <v>259</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="50"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="37"/>
     </row>
     <row r="2" spans="1:8" ht="19.95" customHeight="1">
       <c r="A2" s="4" t="s">
@@ -7984,14 +7987,14 @@
       </c>
     </row>
     <row r="3" spans="1:8" ht="19.95" customHeight="1">
-      <c r="A3" s="44" t="s">
+      <c r="A3" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="44"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
       <c r="G3" s="6">
         <f>SUM(G4:G109)</f>
         <v>3063</v>

--- a/周度_工厂配送兔司家门店货品对比表及销售排行表_格式化模板.xlsx
+++ b/周度_工厂配送兔司家门店货品对比表及销售排行表_格式化模板.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wadec\Documents\projects\mainyan-auto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60A3F250-4E1E-45D9-B8E0-1BA0CC493D15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEFD7F6F-2269-49E1-91AE-23F83F2421FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1536" yWindow="1536" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="配送门店业绩表 5.25-5.31" sheetId="4" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1127" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1125" uniqueCount="267">
   <si>
     <t>序号</t>
   </si>
@@ -56,12 +56,6 @@
   </si>
   <si>
     <t>合计</t>
-  </si>
-  <si>
-    <t>焙满香滨江店</t>
-  </si>
-  <si>
-    <t>兔司家白云尚城店</t>
   </si>
   <si>
     <t>2026年5月25日至5月31日工厂配送兔司家门店货品对比表及各商品大类销售排行表</t>
@@ -1031,7 +1025,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -1118,52 +1112,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1257,6 +1212,24 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1266,11 +1239,20 @@
     <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1284,52 +1266,19 @@
     <xf numFmtId="176" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1842,23 +1791,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="22" customFormat="1" ht="36" customHeight="1">
-      <c r="A1" s="31" t="s">
-        <v>268</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="33"/>
-      <c r="K1" s="33"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
+      <c r="A1" s="37" t="s">
+        <v>266</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="39"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
       <c r="P1" s="21"/>
       <c r="Q1" s="21"/>
     </row>
@@ -1870,10 +1819,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D2" s="25" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E2" s="26" t="s">
         <v>2</v>
@@ -1888,19 +1837,19 @@
         <v>5</v>
       </c>
       <c r="I2" s="27" t="s">
+        <v>262</v>
+      </c>
+      <c r="J2" s="27" t="s">
+        <v>263</v>
+      </c>
+      <c r="K2" s="28" t="s">
         <v>264</v>
-      </c>
-      <c r="J2" s="27" t="s">
-        <v>265</v>
-      </c>
-      <c r="K2" s="28" t="s">
-        <v>266</v>
       </c>
       <c r="L2" s="28" t="s">
         <v>6</v>
       </c>
       <c r="M2" s="27" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="N2" s="28" t="s">
         <v>7</v>
@@ -1910,57 +1859,59 @@
       </c>
     </row>
     <row r="3" spans="1:17" ht="22.05" customHeight="1">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="35"/>
-      <c r="C3" s="47">
+      <c r="B3" s="52"/>
+      <c r="C3" s="31">
         <f>SUM(C4:C5)</f>
-        <v>7226.4400000000005</v>
-      </c>
-      <c r="D3" s="47">
+        <v>0</v>
+      </c>
+      <c r="D3" s="31">
         <f>SUM(D4:D5)</f>
-        <v>7046.4400000000005</v>
-      </c>
-      <c r="E3" s="48">
+        <v>0</v>
+      </c>
+      <c r="E3" s="32">
         <f>SUM(E4:E5)</f>
-        <v>2</v>
-      </c>
-      <c r="F3" s="48">
+        <v>0</v>
+      </c>
+      <c r="F3" s="32">
         <f>SUM(F4:F5)</f>
-        <v>180</v>
-      </c>
-      <c r="G3" s="49">
-        <v>9781</v>
-      </c>
-      <c r="H3" s="49">
-        <v>16508.3</v>
-      </c>
-      <c r="I3" s="50">
+        <v>0</v>
+      </c>
+      <c r="G3" s="32">
+        <f>SUM(G4:G5)</f>
+        <v>0</v>
+      </c>
+      <c r="H3" s="32">
+        <f>SUM(H4:H5)</f>
+        <v>0</v>
+      </c>
+      <c r="I3" s="33">
         <f t="shared" ref="I3:O3" si="0">SUM(I4:I5)</f>
-        <v>2</v>
-      </c>
-      <c r="J3" s="50">
+        <v>0</v>
+      </c>
+      <c r="J3" s="33">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K3" s="50">
-        <f t="shared" si="0"/>
-        <v>672</v>
-      </c>
-      <c r="L3" s="50">
+      <c r="K3" s="33">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M3" s="50">
+      <c r="L3" s="33">
         <f t="shared" si="0"/>
-        <v>672</v>
-      </c>
-      <c r="N3" s="50">
+        <v>0</v>
+      </c>
+      <c r="M3" s="33">
         <f t="shared" si="0"/>
-        <v>7226.4400000000005</v>
-      </c>
-      <c r="O3" s="50">
+        <v>0</v>
+      </c>
+      <c r="N3" s="33">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O3" s="33">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -1970,85 +1921,51 @@
         <f>ROW()-3</f>
         <v>1</v>
       </c>
-      <c r="B4" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="51">
-        <v>5912.14</v>
-      </c>
-      <c r="D4" s="47">
+      <c r="B4" s="23"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="31">
         <f>C4-F4</f>
-        <v>5812.14</v>
-      </c>
-      <c r="E4" s="48">
-        <v>1</v>
-      </c>
-      <c r="F4" s="48">
-        <v>100</v>
-      </c>
-      <c r="G4" s="52"/>
-      <c r="H4" s="52"/>
-      <c r="I4" s="53">
-        <v>1</v>
-      </c>
-      <c r="J4" s="53"/>
-      <c r="K4" s="53">
-        <v>604</v>
-      </c>
-      <c r="L4" s="53"/>
-      <c r="M4" s="53">
-        <v>604</v>
-      </c>
-      <c r="N4" s="54">
-        <v>5912.14</v>
-      </c>
-      <c r="O4" s="53"/>
+        <v>0</v>
+      </c>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="35"/>
+      <c r="J4" s="35"/>
+      <c r="K4" s="35"/>
+      <c r="L4" s="35"/>
+      <c r="M4" s="35"/>
+      <c r="N4" s="36"/>
+      <c r="O4" s="35"/>
     </row>
     <row r="5" spans="1:17" ht="22.05" customHeight="1">
       <c r="A5" s="28">
         <f t="shared" ref="A5" si="1">ROW()-3</f>
         <v>2</v>
       </c>
-      <c r="B5" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="51">
-        <v>1314.3</v>
-      </c>
-      <c r="D5" s="47">
+      <c r="B5" s="23"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="31">
         <f t="shared" ref="D5" si="2">C5-F5</f>
-        <v>1234.3</v>
-      </c>
-      <c r="E5" s="48">
-        <v>1</v>
-      </c>
-      <c r="F5" s="48">
-        <v>80</v>
-      </c>
-      <c r="G5" s="55"/>
-      <c r="H5" s="55"/>
-      <c r="I5" s="53">
-        <v>1</v>
-      </c>
-      <c r="J5" s="53"/>
-      <c r="K5" s="53">
-        <v>68</v>
-      </c>
-      <c r="L5" s="53"/>
-      <c r="M5" s="53">
-        <v>68</v>
-      </c>
-      <c r="N5" s="54">
-        <v>1314.3</v>
-      </c>
-      <c r="O5" s="53"/>
+        <v>0</v>
+      </c>
+      <c r="E5" s="32"/>
+      <c r="F5" s="32"/>
+      <c r="G5" s="53"/>
+      <c r="H5" s="53"/>
+      <c r="I5" s="35"/>
+      <c r="J5" s="35"/>
+      <c r="K5" s="35"/>
+      <c r="L5" s="35"/>
+      <c r="M5" s="35"/>
+      <c r="N5" s="36"/>
+      <c r="O5" s="35"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="2">
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="G3:G5"/>
-    <mergeCell ref="H3:H5"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2091,174 +2008,174 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" s="10" customFormat="1" ht="25.05" customHeight="1">
-      <c r="A1" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="36"/>
-      <c r="L1" s="37"/>
-      <c r="M1" s="36"/>
-      <c r="N1" s="37"/>
-      <c r="O1" s="36"/>
-      <c r="P1" s="37"/>
-      <c r="Q1" s="36"/>
-      <c r="R1" s="37"/>
-      <c r="S1" s="36"/>
-      <c r="T1" s="37"/>
-      <c r="U1" s="36"/>
-      <c r="V1" s="37"/>
-      <c r="W1" s="36"/>
-      <c r="X1" s="37"/>
-      <c r="Y1" s="36"/>
-      <c r="Z1" s="37"/>
+      <c r="A1" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="46"/>
+      <c r="K1" s="45"/>
+      <c r="L1" s="46"/>
+      <c r="M1" s="45"/>
+      <c r="N1" s="46"/>
+      <c r="O1" s="45"/>
+      <c r="P1" s="46"/>
+      <c r="Q1" s="45"/>
+      <c r="R1" s="46"/>
+      <c r="S1" s="45"/>
+      <c r="T1" s="46"/>
+      <c r="U1" s="45"/>
+      <c r="V1" s="46"/>
+      <c r="W1" s="45"/>
+      <c r="X1" s="46"/>
+      <c r="Y1" s="45"/>
+      <c r="Z1" s="46"/>
       <c r="AA1" s="11"/>
       <c r="AB1" s="12"/>
     </row>
     <row r="2" spans="1:28" ht="19.95" customHeight="1">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="42" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="45" t="s">
+      <c r="E2" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="45" t="s">
+      <c r="F2" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="45" t="s">
+      <c r="G2" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="48"/>
+      <c r="I2" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="45" t="s">
+      <c r="J2" s="49"/>
+      <c r="K2" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="38" t="s">
+      <c r="L2" s="49"/>
+      <c r="M2" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" s="50"/>
+      <c r="O2" s="40" t="s">
+        <v>19</v>
+      </c>
+      <c r="P2" s="50"/>
+      <c r="Q2" s="40" t="s">
+        <v>20</v>
+      </c>
+      <c r="R2" s="50"/>
+      <c r="S2" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="T2" s="50"/>
+      <c r="U2" s="40" t="s">
+        <v>22</v>
+      </c>
+      <c r="V2" s="50"/>
+      <c r="W2" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="X2" s="50"/>
+      <c r="Y2" s="42" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z2" s="49"/>
+    </row>
+    <row r="3" spans="1:28" ht="19.95" customHeight="1">
+      <c r="A3" s="41"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="L3" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="N3" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="O3" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="P3" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q3" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="R3" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="S3" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="T3" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="U3" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="V3" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="W3" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="X3" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y3" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z3" s="15" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" ht="19.95" customHeight="1">
+      <c r="A4" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="39"/>
-      <c r="I2" s="40" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="41"/>
-      <c r="K2" s="40" t="s">
-        <v>19</v>
-      </c>
-      <c r="L2" s="41"/>
-      <c r="M2" s="42" t="s">
-        <v>20</v>
-      </c>
-      <c r="N2" s="43"/>
-      <c r="O2" s="42" t="s">
-        <v>21</v>
-      </c>
-      <c r="P2" s="43"/>
-      <c r="Q2" s="42" t="s">
-        <v>22</v>
-      </c>
-      <c r="R2" s="43"/>
-      <c r="S2" s="42" t="s">
-        <v>23</v>
-      </c>
-      <c r="T2" s="43"/>
-      <c r="U2" s="42" t="s">
-        <v>24</v>
-      </c>
-      <c r="V2" s="43"/>
-      <c r="W2" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="X2" s="43"/>
-      <c r="Y2" s="40" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z2" s="41"/>
-    </row>
-    <row r="3" spans="1:28" ht="19.95" customHeight="1">
-      <c r="A3" s="44"/>
-      <c r="B3" s="40"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J3" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="L3" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="M3" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="N3" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="O3" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="P3" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q3" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="R3" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="S3" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="T3" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="U3" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="V3" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="W3" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="X3" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y3" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="Z3" s="15" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:28" ht="19.95" customHeight="1">
-      <c r="A4" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="42"/>
-      <c r="C4" s="42"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="42"/>
-      <c r="F4" s="42"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
       <c r="G4" s="6">
         <f t="shared" ref="G4:L4" si="0">SUM(G5:G110)</f>
         <v>3063</v>
@@ -2346,19 +2263,19 @@
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="F5" s="8" t="s">
         <v>31</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>33</v>
       </c>
       <c r="G5" s="8">
         <v>8</v>
@@ -2423,19 +2340,19 @@
         <v>2</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="F6" s="8" t="s">
         <v>35</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>37</v>
       </c>
       <c r="G6" s="8">
         <v>408</v>
@@ -2476,19 +2393,19 @@
         <v>3</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D7" s="4" t="s">
+      <c r="F7" s="8" t="s">
         <v>39</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>41</v>
       </c>
       <c r="G7" s="8">
         <v>24</v>
@@ -2541,19 +2458,19 @@
         <v>4</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C8" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="F8" s="8" t="s">
         <v>35</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>37</v>
       </c>
       <c r="G8" s="8">
         <v>312</v>
@@ -2598,19 +2515,19 @@
         <v>5</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C9" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F9" s="8" t="s">
         <v>35</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>37</v>
       </c>
       <c r="G9" s="8">
         <v>1080</v>
@@ -2647,19 +2564,19 @@
         <v>6</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>48</v>
-      </c>
       <c r="F10" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G10" s="8">
         <v>31</v>
@@ -2712,19 +2629,19 @@
         <v>7</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G11" s="8">
         <v>21</v>
@@ -2777,19 +2694,19 @@
         <v>8</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>52</v>
-      </c>
       <c r="F12" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G12" s="8">
         <v>20</v>
@@ -2826,19 +2743,19 @@
         <v>9</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C13" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F13" s="8" t="s">
         <v>35</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>37</v>
       </c>
       <c r="G13" s="8">
         <v>60</v>
@@ -2879,19 +2796,19 @@
         <v>10</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="F14" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G14" s="8">
         <v>5</v>
@@ -2944,19 +2861,19 @@
         <v>11</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D15" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F15" s="8" t="s">
         <v>39</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>41</v>
       </c>
       <c r="G15" s="8">
         <v>7</v>
@@ -3005,19 +2922,19 @@
         <v>12</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C16" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F16" s="8" t="s">
         <v>35</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>37</v>
       </c>
       <c r="G16" s="8">
         <v>120</v>
@@ -3054,19 +2971,19 @@
         <v>13</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G17" s="8">
         <v>13</v>
@@ -3107,19 +3024,19 @@
         <v>14</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D18" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F18" s="8" t="s">
         <v>39</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>41</v>
       </c>
       <c r="G18" s="8">
         <v>5</v>
@@ -3160,19 +3077,19 @@
         <v>15</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G19" s="8">
         <v>9</v>
@@ -3217,19 +3134,19 @@
         <v>16</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D20" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E20" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="E20" s="4" t="s">
-        <v>69</v>
-      </c>
       <c r="F20" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G20" s="8">
         <v>11</v>
@@ -3270,19 +3187,19 @@
         <v>17</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D21" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F21" s="8" t="s">
         <v>39</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>41</v>
       </c>
       <c r="G21" s="8">
         <v>5</v>
@@ -3335,19 +3252,19 @@
         <v>18</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G22" s="8">
         <v>11</v>
@@ -3396,19 +3313,19 @@
         <v>19</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C23" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="F23" s="8" t="s">
         <v>35</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>37</v>
       </c>
       <c r="G23" s="8">
         <v>48</v>
@@ -3445,19 +3362,19 @@
         <v>20</v>
       </c>
       <c r="B24" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F24" s="8" t="s">
         <v>75</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>77</v>
       </c>
       <c r="G24" s="8">
         <v>3</v>
@@ -3502,19 +3419,19 @@
         <v>21</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G25" s="8">
         <v>10</v>
@@ -3563,19 +3480,19 @@
         <v>22</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G26" s="8">
         <v>5</v>
@@ -3620,19 +3537,19 @@
         <v>23</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G27" s="8">
         <v>4</v>
@@ -3673,19 +3590,19 @@
         <v>24</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G28" s="8">
         <v>7</v>
@@ -3734,19 +3651,19 @@
         <v>25</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G29" s="8">
         <v>5</v>
@@ -3795,19 +3712,19 @@
         <v>26</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G30" s="8">
         <v>5</v>
@@ -3844,19 +3761,19 @@
         <v>27</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C31" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F31" s="8" t="s">
         <v>35</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="F31" s="8" t="s">
-        <v>37</v>
       </c>
       <c r="G31" s="8">
         <v>72</v>
@@ -3893,19 +3810,19 @@
         <v>28</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C32" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F32" s="8" t="s">
         <v>35</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="F32" s="8" t="s">
-        <v>37</v>
       </c>
       <c r="G32" s="8">
         <v>64</v>
@@ -3942,19 +3859,19 @@
         <v>29</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G33" s="8">
         <v>3</v>
@@ -3995,19 +3912,19 @@
         <v>30</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G34" s="8">
         <v>3</v>
@@ -4048,19 +3965,19 @@
         <v>31</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C35" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="F35" s="8" t="s">
         <v>35</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="F35" s="8" t="s">
-        <v>37</v>
       </c>
       <c r="G35" s="8">
         <v>32</v>
@@ -4097,19 +4014,19 @@
         <v>32</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G36" s="8">
         <v>5</v>
@@ -4146,19 +4063,19 @@
         <v>33</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G37" s="8">
         <v>3</v>
@@ -4195,19 +4112,19 @@
         <v>34</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G38" s="8">
         <v>1</v>
@@ -4244,19 +4161,19 @@
         <v>35</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G39" s="8">
         <v>4</v>
@@ -4297,19 +4214,19 @@
         <v>36</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G40" s="8">
         <v>10</v>
@@ -4346,19 +4263,19 @@
         <v>37</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G41" s="8">
         <v>3</v>
@@ -4395,19 +4312,19 @@
         <v>38</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C42" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="F42" s="8" t="s">
         <v>35</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E42" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="F42" s="8" t="s">
-        <v>37</v>
       </c>
       <c r="G42" s="8">
         <v>144</v>
@@ -4444,19 +4361,19 @@
         <v>39</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G43" s="8">
         <v>4</v>
@@ -4497,19 +4414,19 @@
         <v>40</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C44" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="F44" s="8" t="s">
         <v>35</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E44" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="F44" s="8" t="s">
-        <v>37</v>
       </c>
       <c r="G44" s="8">
         <v>12</v>
@@ -4546,19 +4463,19 @@
         <v>41</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G45" s="8">
         <v>2</v>
@@ -4595,19 +4512,19 @@
         <v>42</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G46" s="8">
         <v>1</v>
@@ -4644,19 +4561,19 @@
         <v>43</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C47" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="F47" s="8" t="s">
         <v>35</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E47" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="F47" s="8" t="s">
-        <v>37</v>
       </c>
       <c r="G47" s="8">
         <v>12</v>
@@ -4693,19 +4610,19 @@
         <v>44</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G48" s="8">
         <v>2</v>
@@ -4742,19 +4659,19 @@
         <v>45</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D49" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F49" s="8" t="s">
         <v>39</v>
-      </c>
-      <c r="E49" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F49" s="8" t="s">
-        <v>41</v>
       </c>
       <c r="G49" s="8">
         <v>1</v>
@@ -4791,19 +4708,19 @@
         <v>46</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G50" s="8">
         <v>1</v>
@@ -4840,19 +4757,19 @@
         <v>47</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D51" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="F51" s="8" t="s">
         <v>39</v>
-      </c>
-      <c r="E51" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="F51" s="8" t="s">
-        <v>41</v>
       </c>
       <c r="G51" s="8">
         <v>2</v>
@@ -4889,19 +4806,19 @@
         <v>48</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G52" s="8">
         <v>1</v>
@@ -4938,19 +4855,19 @@
         <v>49</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G53" s="8">
         <v>1</v>
@@ -4987,19 +4904,19 @@
         <v>50</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G54" s="8">
         <v>2</v>
@@ -5036,19 +4953,19 @@
         <v>51</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G55" s="8">
         <v>1</v>
@@ -5085,19 +5002,19 @@
         <v>52</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G56" s="8">
         <v>1</v>
@@ -5134,19 +5051,19 @@
         <v>53</v>
       </c>
       <c r="B57" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D57" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="C57" s="4" t="s">
+      <c r="E57" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="D57" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="E57" s="4" t="s">
-        <v>132</v>
-      </c>
       <c r="F57" s="8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G57" s="8">
         <v>100</v>
@@ -5183,19 +5100,19 @@
         <v>54</v>
       </c>
       <c r="B58" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E58" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="C58" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="D58" s="4" t="s">
+      <c r="F58" s="8" t="s">
         <v>134</v>
-      </c>
-      <c r="E58" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="F58" s="8" t="s">
-        <v>136</v>
       </c>
       <c r="G58" s="8">
         <v>25</v>
@@ -5244,19 +5161,19 @@
         <v>55</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D59" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="F59" s="8" t="s">
         <v>134</v>
-      </c>
-      <c r="E59" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="F59" s="8" t="s">
-        <v>136</v>
       </c>
       <c r="G59" s="8">
         <v>13</v>
@@ -5305,19 +5222,19 @@
         <v>56</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D60" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="F60" s="8" t="s">
         <v>134</v>
-      </c>
-      <c r="E60" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="F60" s="8" t="s">
-        <v>136</v>
       </c>
       <c r="G60" s="8">
         <v>31</v>
@@ -5370,19 +5287,19 @@
         <v>57</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D61" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="F61" s="8" t="s">
         <v>134</v>
-      </c>
-      <c r="E61" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="F61" s="8" t="s">
-        <v>136</v>
       </c>
       <c r="G61" s="8">
         <v>9</v>
@@ -5427,19 +5344,19 @@
         <v>58</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D62" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F62" s="8" t="s">
         <v>134</v>
-      </c>
-      <c r="E62" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="F62" s="8" t="s">
-        <v>136</v>
       </c>
       <c r="G62" s="8">
         <v>6</v>
@@ -5480,19 +5397,19 @@
         <v>59</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D63" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="F63" s="8" t="s">
         <v>134</v>
-      </c>
-      <c r="E63" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="F63" s="8" t="s">
-        <v>136</v>
       </c>
       <c r="G63" s="8">
         <v>9</v>
@@ -5533,19 +5450,19 @@
         <v>60</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D64" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="F64" s="8" t="s">
         <v>134</v>
-      </c>
-      <c r="E64" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="F64" s="8" t="s">
-        <v>136</v>
       </c>
       <c r="G64" s="8">
         <v>5</v>
@@ -5586,19 +5503,19 @@
         <v>61</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D65" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F65" s="8" t="s">
         <v>134</v>
-      </c>
-      <c r="E65" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="F65" s="8" t="s">
-        <v>136</v>
       </c>
       <c r="G65" s="8">
         <v>3</v>
@@ -5639,19 +5556,19 @@
         <v>62</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D66" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="F66" s="8" t="s">
         <v>134</v>
-      </c>
-      <c r="E66" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="F66" s="8" t="s">
-        <v>136</v>
       </c>
       <c r="G66" s="8">
         <v>3</v>
@@ -5688,19 +5605,19 @@
         <v>63</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F67" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G67" s="8">
         <v>3</v>
@@ -5737,19 +5654,19 @@
         <v>64</v>
       </c>
       <c r="B68" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="D68" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="C68" s="4" t="s">
+      <c r="E68" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="D68" s="4" t="s">
+      <c r="F68" s="8" t="s">
         <v>153</v>
-      </c>
-      <c r="E68" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="F68" s="8" t="s">
-        <v>155</v>
       </c>
       <c r="G68" s="8">
         <v>8</v>
@@ -5786,19 +5703,19 @@
         <v>65</v>
       </c>
       <c r="B69" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="E69" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="C69" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="D69" s="4" t="s">
+      <c r="F69" s="8" t="s">
         <v>157</v>
-      </c>
-      <c r="E69" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="F69" s="8" t="s">
-        <v>159</v>
       </c>
       <c r="G69" s="8">
         <v>6</v>
@@ -5835,19 +5752,19 @@
         <v>66</v>
       </c>
       <c r="B70" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="E70" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="F70" s="8" t="s">
         <v>160</v>
-      </c>
-      <c r="C70" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="D70" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="E70" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="F70" s="8" t="s">
-        <v>162</v>
       </c>
       <c r="G70" s="8">
         <v>5</v>
@@ -5884,19 +5801,19 @@
         <v>67</v>
       </c>
       <c r="B71" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="D71" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="C71" s="4" t="s">
+      <c r="E71" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="D71" s="4" t="s">
+      <c r="F71" s="8" t="s">
         <v>165</v>
-      </c>
-      <c r="E71" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="F71" s="8" t="s">
-        <v>167</v>
       </c>
       <c r="G71" s="8">
         <v>8</v>
@@ -5937,19 +5854,19 @@
         <v>68</v>
       </c>
       <c r="B72" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="E72" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="C72" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="D72" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="E72" s="4" t="s">
-        <v>170</v>
-      </c>
       <c r="F72" s="8" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G72" s="8">
         <v>4</v>
@@ -5990,19 +5907,19 @@
         <v>69</v>
       </c>
       <c r="B73" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="E73" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="C73" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="D73" s="4" t="s">
+      <c r="F73" s="8" t="s">
         <v>172</v>
-      </c>
-      <c r="E73" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="F73" s="8" t="s">
-        <v>174</v>
       </c>
       <c r="G73" s="8">
         <v>50</v>
@@ -6043,19 +5960,19 @@
         <v>70</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D74" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="F74" s="8" t="s">
         <v>165</v>
-      </c>
-      <c r="E74" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="F74" s="8" t="s">
-        <v>167</v>
       </c>
       <c r="G74" s="8">
         <v>2</v>
@@ -6096,19 +6013,19 @@
         <v>71</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F75" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G75" s="8">
         <v>24</v>
@@ -6145,19 +6062,19 @@
         <v>72</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D76" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="E76" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="F76" s="8" t="s">
         <v>165</v>
-      </c>
-      <c r="E76" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="F76" s="8" t="s">
-        <v>167</v>
       </c>
       <c r="G76" s="8">
         <v>2</v>
@@ -6198,19 +6115,19 @@
         <v>73</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D77" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="E77" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="F77" s="8" t="s">
         <v>165</v>
-      </c>
-      <c r="E77" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="F77" s="8" t="s">
-        <v>167</v>
       </c>
       <c r="G77" s="8">
         <v>3</v>
@@ -6251,19 +6168,19 @@
         <v>74</v>
       </c>
       <c r="B78" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="E78" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="C78" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="D78" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="E78" s="4" t="s">
-        <v>185</v>
-      </c>
       <c r="F78" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G78" s="8">
         <v>6</v>
@@ -6304,19 +6221,19 @@
         <v>75</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F79" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G79" s="8">
         <v>12</v>
@@ -6353,19 +6270,19 @@
         <v>76</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D80" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="E80" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="F80" s="8" t="s">
         <v>165</v>
-      </c>
-      <c r="E80" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="F80" s="8" t="s">
-        <v>167</v>
       </c>
       <c r="G80" s="8">
         <v>3</v>
@@ -6406,19 +6323,19 @@
         <v>77</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D81" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="F81" s="8" t="s">
         <v>165</v>
-      </c>
-      <c r="E81" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="F81" s="8" t="s">
-        <v>167</v>
       </c>
       <c r="G81" s="8">
         <v>2</v>
@@ -6459,19 +6376,19 @@
         <v>78</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D82" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="E82" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="F82" s="8" t="s">
         <v>165</v>
-      </c>
-      <c r="E82" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="F82" s="8" t="s">
-        <v>167</v>
       </c>
       <c r="G82" s="8">
         <v>2</v>
@@ -6512,19 +6429,19 @@
         <v>79</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F83" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G83" s="8">
         <v>23</v>
@@ -6569,19 +6486,19 @@
         <v>80</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F84" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G84" s="8">
         <v>4</v>
@@ -6622,19 +6539,19 @@
         <v>81</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D85" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="E85" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="F85" s="8" t="s">
         <v>165</v>
-      </c>
-      <c r="E85" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="F85" s="8" t="s">
-        <v>167</v>
       </c>
       <c r="G85" s="8">
         <v>1</v>
@@ -6671,19 +6588,19 @@
         <v>82</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D86" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="E86" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="F86" s="8" t="s">
         <v>165</v>
-      </c>
-      <c r="E86" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="F86" s="8" t="s">
-        <v>167</v>
       </c>
       <c r="G86" s="8">
         <v>1</v>
@@ -6720,19 +6637,19 @@
         <v>83</v>
       </c>
       <c r="B87" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="E87" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="C87" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="D87" s="4" t="s">
+      <c r="F87" s="8" t="s">
         <v>203</v>
-      </c>
-      <c r="E87" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="F87" s="8" t="s">
-        <v>205</v>
       </c>
       <c r="G87" s="8">
         <v>5</v>
@@ -6773,19 +6690,19 @@
         <v>84</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F88" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G88" s="8">
         <v>2</v>
@@ -6822,19 +6739,19 @@
         <v>85</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F89" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G89" s="8">
         <v>2</v>
@@ -6875,19 +6792,19 @@
         <v>86</v>
       </c>
       <c r="B90" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="E90" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="C90" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="D90" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="E90" s="4" t="s">
-        <v>212</v>
-      </c>
       <c r="F90" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G90" s="8">
         <v>1</v>
@@ -6924,19 +6841,19 @@
         <v>87</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D91" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="E91" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="F91" s="8" t="s">
         <v>203</v>
-      </c>
-      <c r="E91" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="F91" s="8" t="s">
-        <v>205</v>
       </c>
       <c r="G91" s="8">
         <v>3</v>
@@ -6973,19 +6890,19 @@
         <v>88</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F92" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G92" s="8">
         <v>2</v>
@@ -7022,19 +6939,19 @@
         <v>89</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F93" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G93" s="8">
         <v>3</v>
@@ -7071,19 +6988,19 @@
         <v>90</v>
       </c>
       <c r="B94" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="D94" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="E94" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="C94" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="D94" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="E94" s="4" t="s">
-        <v>220</v>
-      </c>
       <c r="F94" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G94" s="8">
         <v>2</v>
@@ -7120,19 +7037,19 @@
         <v>91</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F95" s="8" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G95" s="8">
         <v>3</v>
@@ -7169,19 +7086,19 @@
         <v>92</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F96" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G96" s="8">
         <v>1</v>
@@ -7218,19 +7135,19 @@
         <v>93</v>
       </c>
       <c r="B97" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="E97" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="C97" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="D97" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="E97" s="4" t="s">
-        <v>227</v>
-      </c>
       <c r="F97" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G97" s="8">
         <v>5</v>
@@ -7267,19 +7184,19 @@
         <v>94</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D98" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="E98" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="F98" s="8" t="s">
         <v>203</v>
-      </c>
-      <c r="E98" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="F98" s="8" t="s">
-        <v>205</v>
       </c>
       <c r="G98" s="8">
         <v>1</v>
@@ -7316,19 +7233,19 @@
         <v>95</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D99" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="E99" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="F99" s="8" t="s">
         <v>203</v>
-      </c>
-      <c r="E99" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="F99" s="8" t="s">
-        <v>205</v>
       </c>
       <c r="G99" s="8">
         <v>2</v>
@@ -7365,19 +7282,19 @@
         <v>96</v>
       </c>
       <c r="B100" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="E100" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="C100" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="D100" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="E100" s="4" t="s">
-        <v>234</v>
-      </c>
       <c r="F100" s="8" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G100" s="8">
         <v>8</v>
@@ -7414,19 +7331,19 @@
         <v>97</v>
       </c>
       <c r="B101" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="E101" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="F101" s="8" t="s">
         <v>235</v>
-      </c>
-      <c r="C101" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="D101" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="E101" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="F101" s="8" t="s">
-        <v>237</v>
       </c>
       <c r="G101" s="8">
         <v>1</v>
@@ -7463,19 +7380,19 @@
         <v>98</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F102" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G102" s="8">
         <v>1</v>
@@ -7512,19 +7429,19 @@
         <v>99</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F103" s="8" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="G103" s="8">
         <v>3</v>
@@ -7561,19 +7478,19 @@
         <v>100</v>
       </c>
       <c r="B104" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="D104" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="C104" s="4" t="s">
+      <c r="E104" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="D104" s="4" t="s">
+      <c r="F104" s="8" t="s">
         <v>244</v>
-      </c>
-      <c r="E104" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="F104" s="8" t="s">
-        <v>246</v>
       </c>
       <c r="G104" s="8">
         <v>4</v>
@@ -7618,19 +7535,19 @@
         <v>101</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D105" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="E105" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="F105" s="8" t="s">
         <v>244</v>
-      </c>
-      <c r="E105" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="F105" s="8" t="s">
-        <v>246</v>
       </c>
       <c r="G105" s="8">
         <v>5</v>
@@ -7667,19 +7584,19 @@
         <v>102</v>
       </c>
       <c r="B106" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="D106" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="E106" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="C106" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="D106" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="E106" s="4" t="s">
-        <v>251</v>
-      </c>
       <c r="F106" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G106" s="8">
         <v>5</v>
@@ -7716,19 +7633,19 @@
         <v>103</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D107" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="E107" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="F107" s="8" t="s">
         <v>244</v>
-      </c>
-      <c r="E107" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="F107" s="8" t="s">
-        <v>246</v>
       </c>
       <c r="G107" s="8">
         <v>2</v>
@@ -7765,19 +7682,19 @@
         <v>104</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F108" s="8" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G108" s="8">
         <v>2</v>
@@ -7814,19 +7731,19 @@
         <v>105</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F109" s="8" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G109" s="8">
         <v>2</v>
@@ -7863,19 +7780,19 @@
         <v>106</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F110" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G110" s="8">
         <v>1</v>
@@ -7908,13 +7825,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
     <mergeCell ref="A1:Z1"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="I2:J2"/>
@@ -7926,6 +7836,13 @@
     <mergeCell ref="U2:V2"/>
     <mergeCell ref="W2:X2"/>
     <mergeCell ref="Y2:Z2"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7949,52 +7866,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1">
-      <c r="A1" s="36" t="s">
-        <v>259</v>
-      </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="37"/>
+      <c r="A1" s="45" t="s">
+        <v>257</v>
+      </c>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="46"/>
     </row>
     <row r="2" spans="1:8" ht="19.95" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="E2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="F2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>17</v>
-      </c>
       <c r="G2" s="6" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="19.95" customHeight="1">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
       <c r="G3" s="6">
         <f>SUM(G4:G109)</f>
         <v>3063</v>
@@ -8010,19 +7927,19 @@
         <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="F4" s="8" t="s">
         <v>35</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>37</v>
       </c>
       <c r="G4" s="8">
         <v>408</v>
@@ -8037,19 +7954,19 @@
         <v>2</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="E5" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="F5" s="8" t="s">
         <v>165</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>167</v>
       </c>
       <c r="G5" s="8">
         <v>8</v>
@@ -8064,19 +7981,19 @@
         <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" s="4" t="s">
+      <c r="F6" s="8" t="s">
         <v>39</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>41</v>
       </c>
       <c r="G6" s="8">
         <v>24</v>
@@ -8091,19 +8008,19 @@
         <v>4</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" s="8" t="s">
         <v>35</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>37</v>
       </c>
       <c r="G7" s="8">
         <v>312</v>
@@ -8118,19 +8035,19 @@
         <v>5</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>170</v>
-      </c>
       <c r="F8" s="8" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G8" s="8">
         <v>4</v>
@@ -8145,19 +8062,19 @@
         <v>6</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="F9" s="8" t="s">
         <v>31</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>33</v>
       </c>
       <c r="G9" s="8">
         <v>8</v>
@@ -8172,19 +8089,19 @@
         <v>7</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C10" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" s="8" t="s">
         <v>35</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>37</v>
       </c>
       <c r="G10" s="8">
         <v>1080</v>
@@ -8199,19 +8116,19 @@
         <v>8</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="D11" s="4" t="s">
+      <c r="F11" s="8" t="s">
         <v>172</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>174</v>
       </c>
       <c r="G11" s="8">
         <v>50</v>
@@ -8226,19 +8143,19 @@
         <v>9</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>48</v>
-      </c>
       <c r="F12" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G12" s="8">
         <v>31</v>
@@ -8253,19 +8170,19 @@
         <v>10</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G13" s="8">
         <v>21</v>
@@ -8280,19 +8197,19 @@
         <v>11</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D14" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="F14" s="8" t="s">
         <v>165</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>167</v>
       </c>
       <c r="G14" s="8">
         <v>2</v>
@@ -8307,19 +8224,19 @@
         <v>12</v>
       </c>
       <c r="B15" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>52</v>
-      </c>
       <c r="F15" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G15" s="8">
         <v>20</v>
@@ -8334,19 +8251,19 @@
         <v>13</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C16" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F16" s="8" t="s">
         <v>35</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>37</v>
       </c>
       <c r="G16" s="8">
         <v>60</v>
@@ -8361,19 +8278,19 @@
         <v>14</v>
       </c>
       <c r="B17" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E17" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="F17" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G17" s="8">
         <v>5</v>
@@ -8388,19 +8305,19 @@
         <v>15</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D18" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F18" s="8" t="s">
         <v>39</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>41</v>
       </c>
       <c r="G18" s="8">
         <v>7</v>
@@ -8415,19 +8332,19 @@
         <v>16</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G19" s="8">
         <v>24</v>
@@ -8442,19 +8359,19 @@
         <v>17</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C20" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F20" s="8" t="s">
         <v>35</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>37</v>
       </c>
       <c r="G20" s="8">
         <v>120</v>
@@ -8469,19 +8386,19 @@
         <v>18</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G21" s="8">
         <v>13</v>
@@ -8496,19 +8413,19 @@
         <v>19</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D22" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="F22" s="8" t="s">
         <v>165</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>167</v>
       </c>
       <c r="G22" s="8">
         <v>2</v>
@@ -8523,19 +8440,19 @@
         <v>20</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D23" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="F23" s="8" t="s">
         <v>165</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>167</v>
       </c>
       <c r="G23" s="8">
         <v>3</v>
@@ -8550,19 +8467,19 @@
         <v>21</v>
       </c>
       <c r="B24" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="E24" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="C24" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>185</v>
-      </c>
       <c r="F24" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G24" s="8">
         <v>6</v>
@@ -8577,19 +8494,19 @@
         <v>22</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G25" s="8">
         <v>12</v>
@@ -8604,19 +8521,19 @@
         <v>23</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D26" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="F26" s="8" t="s">
         <v>165</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>167</v>
       </c>
       <c r="G26" s="8">
         <v>3</v>
@@ -8631,19 +8548,19 @@
         <v>24</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D27" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F27" s="8" t="s">
         <v>39</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="F27" s="8" t="s">
-        <v>41</v>
       </c>
       <c r="G27" s="8">
         <v>5</v>
@@ -8658,19 +8575,19 @@
         <v>25</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G28" s="8">
         <v>9</v>
@@ -8685,19 +8602,19 @@
         <v>26</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D29" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="F29" s="8" t="s">
         <v>165</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="F29" s="8" t="s">
-        <v>167</v>
       </c>
       <c r="G29" s="8">
         <v>2</v>
@@ -8712,19 +8629,19 @@
         <v>27</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D30" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E30" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="E30" s="4" t="s">
-        <v>69</v>
-      </c>
       <c r="F30" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G30" s="8">
         <v>11</v>
@@ -8739,19 +8656,19 @@
         <v>28</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D31" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F31" s="8" t="s">
         <v>39</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="F31" s="8" t="s">
-        <v>41</v>
       </c>
       <c r="G31" s="8">
         <v>5</v>
@@ -8766,19 +8683,19 @@
         <v>29</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G32" s="8">
         <v>11</v>
@@ -8793,19 +8710,19 @@
         <v>30</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C33" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="F33" s="8" t="s">
         <v>35</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="F33" s="8" t="s">
-        <v>37</v>
       </c>
       <c r="G33" s="8">
         <v>48</v>
@@ -8820,19 +8737,19 @@
         <v>31</v>
       </c>
       <c r="B34" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F34" s="8" t="s">
         <v>75</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="F34" s="8" t="s">
-        <v>77</v>
       </c>
       <c r="G34" s="8">
         <v>3</v>
@@ -8847,19 +8764,19 @@
         <v>32</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G35" s="8">
         <v>10</v>
@@ -8874,19 +8791,19 @@
         <v>33</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G36" s="8">
         <v>5</v>
@@ -8901,19 +8818,19 @@
         <v>34</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G37" s="8">
         <v>4</v>
@@ -8928,19 +8845,19 @@
         <v>35</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D38" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="F38" s="8" t="s">
         <v>165</v>
-      </c>
-      <c r="E38" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="F38" s="8" t="s">
-        <v>167</v>
       </c>
       <c r="G38" s="8">
         <v>2</v>
@@ -8955,19 +8872,19 @@
         <v>36</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G39" s="8">
         <v>23</v>
@@ -8982,19 +8899,19 @@
         <v>37</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G40" s="8">
         <v>7</v>
@@ -9009,19 +8926,19 @@
         <v>38</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G41" s="8">
         <v>5</v>
@@ -9036,19 +8953,19 @@
         <v>39</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G42" s="8">
         <v>4</v>
@@ -9063,19 +8980,19 @@
         <v>40</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D43" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="F43" s="8" t="s">
         <v>165</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="F43" s="8" t="s">
-        <v>167</v>
       </c>
       <c r="G43" s="8">
         <v>1</v>
@@ -9090,19 +9007,19 @@
         <v>41</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G44" s="8">
         <v>5</v>
@@ -9117,19 +9034,19 @@
         <v>42</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C45" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F45" s="8" t="s">
         <v>35</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="F45" s="8" t="s">
-        <v>37</v>
       </c>
       <c r="G45" s="8">
         <v>72</v>
@@ -9144,19 +9061,19 @@
         <v>43</v>
       </c>
       <c r="B46" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="D46" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="E46" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="F46" s="8" t="s">
         <v>244</v>
-      </c>
-      <c r="E46" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="F46" s="8" t="s">
-        <v>246</v>
       </c>
       <c r="G46" s="8">
         <v>4</v>
@@ -9171,19 +9088,19 @@
         <v>44</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D47" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="F47" s="8" t="s">
         <v>165</v>
-      </c>
-      <c r="E47" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="F47" s="8" t="s">
-        <v>167</v>
       </c>
       <c r="G47" s="8">
         <v>1</v>
@@ -9198,19 +9115,19 @@
         <v>45</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C48" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F48" s="8" t="s">
         <v>35</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E48" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="F48" s="8" t="s">
-        <v>37</v>
       </c>
       <c r="G48" s="8">
         <v>64</v>
@@ -9225,19 +9142,19 @@
         <v>46</v>
       </c>
       <c r="B49" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D49" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="C49" s="4" t="s">
+      <c r="E49" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="D49" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="E49" s="4" t="s">
-        <v>132</v>
-      </c>
       <c r="F49" s="8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G49" s="8">
         <v>100</v>
@@ -9252,19 +9169,19 @@
         <v>47</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D50" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="F50" s="8" t="s">
         <v>244</v>
-      </c>
-      <c r="E50" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="F50" s="8" t="s">
-        <v>246</v>
       </c>
       <c r="G50" s="8">
         <v>5</v>
@@ -9279,19 +9196,19 @@
         <v>48</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G51" s="8">
         <v>3</v>
@@ -9306,19 +9223,19 @@
         <v>49</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G52" s="8">
         <v>3</v>
@@ -9333,19 +9250,19 @@
         <v>50</v>
       </c>
       <c r="B53" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E53" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="C53" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="D53" s="4" t="s">
+      <c r="F53" s="8" t="s">
         <v>134</v>
-      </c>
-      <c r="E53" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="F53" s="8" t="s">
-        <v>136</v>
       </c>
       <c r="G53" s="8">
         <v>25</v>
@@ -9360,19 +9277,19 @@
         <v>51</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C54" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="F54" s="8" t="s">
         <v>35</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E54" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="F54" s="8" t="s">
-        <v>37</v>
       </c>
       <c r="G54" s="8">
         <v>32</v>
@@ -9387,19 +9304,19 @@
         <v>52</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D55" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="F55" s="8" t="s">
         <v>134</v>
-      </c>
-      <c r="E55" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="F55" s="8" t="s">
-        <v>136</v>
       </c>
       <c r="G55" s="8">
         <v>13</v>
@@ -9414,19 +9331,19 @@
         <v>53</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G56" s="8">
         <v>5</v>
@@ -9441,19 +9358,19 @@
         <v>54</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G57" s="8">
         <v>3</v>
@@ -9468,19 +9385,19 @@
         <v>55</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G58" s="8">
         <v>1</v>
@@ -9495,19 +9412,19 @@
         <v>56</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G59" s="8">
         <v>4</v>
@@ -9522,19 +9439,19 @@
         <v>57</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D60" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="F60" s="8" t="s">
         <v>134</v>
-      </c>
-      <c r="E60" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="F60" s="8" t="s">
-        <v>136</v>
       </c>
       <c r="G60" s="8">
         <v>31</v>
@@ -9549,19 +9466,19 @@
         <v>58</v>
       </c>
       <c r="B61" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="E61" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="C61" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="D61" s="4" t="s">
+      <c r="F61" s="8" t="s">
         <v>203</v>
-      </c>
-      <c r="E61" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="F61" s="8" t="s">
-        <v>205</v>
       </c>
       <c r="G61" s="8">
         <v>5</v>
@@ -9576,19 +9493,19 @@
         <v>59</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G62" s="8">
         <v>10</v>
@@ -9603,19 +9520,19 @@
         <v>60</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F63" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G63" s="8">
         <v>3</v>
@@ -9630,19 +9547,19 @@
         <v>61</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F64" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G64" s="8">
         <v>2</v>
@@ -9657,19 +9574,19 @@
         <v>62</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D65" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="F65" s="8" t="s">
         <v>134</v>
-      </c>
-      <c r="E65" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="F65" s="8" t="s">
-        <v>136</v>
       </c>
       <c r="G65" s="8">
         <v>9</v>
@@ -9684,19 +9601,19 @@
         <v>63</v>
       </c>
       <c r="B66" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="D66" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="C66" s="4" t="s">
+      <c r="E66" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="D66" s="4" t="s">
+      <c r="F66" s="8" t="s">
         <v>153</v>
-      </c>
-      <c r="E66" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="F66" s="8" t="s">
-        <v>155</v>
       </c>
       <c r="G66" s="8">
         <v>8</v>
@@ -9711,19 +9628,19 @@
         <v>64</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F67" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G67" s="8">
         <v>2</v>
@@ -9738,19 +9655,19 @@
         <v>65</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C68" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E68" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="F68" s="8" t="s">
         <v>35</v>
-      </c>
-      <c r="D68" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E68" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="F68" s="8" t="s">
-        <v>37</v>
       </c>
       <c r="G68" s="8">
         <v>144</v>
@@ -9765,19 +9682,19 @@
         <v>66</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F69" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G69" s="8">
         <v>4</v>
@@ -9792,19 +9709,19 @@
         <v>67</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C70" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E70" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="F70" s="8" t="s">
         <v>35</v>
-      </c>
-      <c r="D70" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E70" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="F70" s="8" t="s">
-        <v>37</v>
       </c>
       <c r="G70" s="8">
         <v>12</v>
@@ -9819,19 +9736,19 @@
         <v>68</v>
       </c>
       <c r="B71" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="E71" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="C71" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="D71" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="E71" s="4" t="s">
-        <v>212</v>
-      </c>
       <c r="F71" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G71" s="8">
         <v>1</v>
@@ -9846,19 +9763,19 @@
         <v>69</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D72" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="F72" s="8" t="s">
         <v>203</v>
-      </c>
-      <c r="E72" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="F72" s="8" t="s">
-        <v>205</v>
       </c>
       <c r="G72" s="8">
         <v>3</v>
@@ -9873,19 +9790,19 @@
         <v>70</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F73" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G73" s="8">
         <v>2</v>
@@ -9900,19 +9817,19 @@
         <v>71</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F74" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G74" s="8">
         <v>3</v>
@@ -9927,19 +9844,19 @@
         <v>72</v>
       </c>
       <c r="B75" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="E75" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="C75" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="D75" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="E75" s="4" t="s">
-        <v>220</v>
-      </c>
       <c r="F75" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G75" s="8">
         <v>2</v>
@@ -9954,19 +9871,19 @@
         <v>73</v>
       </c>
       <c r="B76" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="E76" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="C76" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="D76" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="E76" s="4" t="s">
-        <v>251</v>
-      </c>
       <c r="F76" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G76" s="8">
         <v>5</v>
@@ -9981,19 +9898,19 @@
         <v>74</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F77" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G77" s="8">
         <v>2</v>
@@ -10008,19 +9925,19 @@
         <v>75</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F78" s="8" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G78" s="8">
         <v>3</v>
@@ -10035,19 +9952,19 @@
         <v>76</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F79" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G79" s="8">
         <v>1</v>
@@ -10062,19 +9979,19 @@
         <v>77</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C80" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E80" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="F80" s="8" t="s">
         <v>35</v>
-      </c>
-      <c r="D80" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E80" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="F80" s="8" t="s">
-        <v>37</v>
       </c>
       <c r="G80" s="8">
         <v>12</v>
@@ -10089,19 +10006,19 @@
         <v>78</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F81" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G81" s="8">
         <v>2</v>
@@ -10116,19 +10033,19 @@
         <v>79</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D82" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E82" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F82" s="8" t="s">
         <v>39</v>
-      </c>
-      <c r="E82" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F82" s="8" t="s">
-        <v>41</v>
       </c>
       <c r="G82" s="8">
         <v>1</v>
@@ -10143,19 +10060,19 @@
         <v>80</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F83" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G83" s="8">
         <v>1</v>
@@ -10170,19 +10087,19 @@
         <v>81</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F84" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G84" s="8">
         <v>1</v>
@@ -10197,19 +10114,19 @@
         <v>82</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D85" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E85" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="F85" s="8" t="s">
         <v>39</v>
-      </c>
-      <c r="E85" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="F85" s="8" t="s">
-        <v>41</v>
       </c>
       <c r="G85" s="8">
         <v>2</v>
@@ -10224,19 +10141,19 @@
         <v>83</v>
       </c>
       <c r="B86" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="E86" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="C86" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="D86" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="E86" s="4" t="s">
-        <v>227</v>
-      </c>
       <c r="F86" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G86" s="8">
         <v>5</v>
@@ -10251,19 +10168,19 @@
         <v>84</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D87" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E87" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F87" s="8" t="s">
         <v>134</v>
-      </c>
-      <c r="E87" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="F87" s="8" t="s">
-        <v>136</v>
       </c>
       <c r="G87" s="8">
         <v>6</v>
@@ -10278,19 +10195,19 @@
         <v>85</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F88" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G88" s="8">
         <v>1</v>
@@ -10305,19 +10222,19 @@
         <v>86</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D89" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E89" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="F89" s="8" t="s">
         <v>134</v>
-      </c>
-      <c r="E89" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="F89" s="8" t="s">
-        <v>136</v>
       </c>
       <c r="G89" s="8">
         <v>9</v>
@@ -10332,19 +10249,19 @@
         <v>87</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F90" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G90" s="8">
         <v>1</v>
@@ -10359,19 +10276,19 @@
         <v>88</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F91" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G91" s="8">
         <v>2</v>
@@ -10386,19 +10303,19 @@
         <v>89</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F92" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G92" s="8">
         <v>1</v>
@@ -10413,19 +10330,19 @@
         <v>90</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D93" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="E93" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="F93" s="8" t="s">
         <v>244</v>
-      </c>
-      <c r="E93" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="F93" s="8" t="s">
-        <v>246</v>
       </c>
       <c r="G93" s="8">
         <v>2</v>
@@ -10440,19 +10357,19 @@
         <v>91</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D94" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="E94" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="F94" s="8" t="s">
         <v>203</v>
-      </c>
-      <c r="E94" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="F94" s="8" t="s">
-        <v>205</v>
       </c>
       <c r="G94" s="8">
         <v>1</v>
@@ -10467,19 +10384,19 @@
         <v>92</v>
       </c>
       <c r="B95" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="E95" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="C95" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="D95" s="4" t="s">
+      <c r="F95" s="8" t="s">
         <v>157</v>
-      </c>
-      <c r="E95" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="F95" s="8" t="s">
-        <v>159</v>
       </c>
       <c r="G95" s="8">
         <v>6</v>
@@ -10494,19 +10411,19 @@
         <v>93</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D96" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="E96" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="F96" s="8" t="s">
         <v>203</v>
-      </c>
-      <c r="E96" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="F96" s="8" t="s">
-        <v>205</v>
       </c>
       <c r="G96" s="8">
         <v>2</v>
@@ -10521,19 +10438,19 @@
         <v>94</v>
       </c>
       <c r="B97" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="E97" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="C97" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="D97" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="E97" s="4" t="s">
-        <v>234</v>
-      </c>
       <c r="F97" s="8" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G97" s="8">
         <v>8</v>
@@ -10548,19 +10465,19 @@
         <v>95</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D98" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E98" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="F98" s="8" t="s">
         <v>134</v>
-      </c>
-      <c r="E98" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="F98" s="8" t="s">
-        <v>136</v>
       </c>
       <c r="G98" s="8">
         <v>5</v>
@@ -10575,19 +10492,19 @@
         <v>96</v>
       </c>
       <c r="B99" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="E99" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="F99" s="8" t="s">
         <v>235</v>
-      </c>
-      <c r="C99" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="D99" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="E99" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="F99" s="8" t="s">
-        <v>237</v>
       </c>
       <c r="G99" s="8">
         <v>1</v>
@@ -10602,19 +10519,19 @@
         <v>97</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F100" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G100" s="8">
         <v>1</v>
@@ -10629,19 +10546,19 @@
         <v>98</v>
       </c>
       <c r="B101" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="E101" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="F101" s="8" t="s">
         <v>160</v>
-      </c>
-      <c r="C101" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="D101" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="E101" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="F101" s="8" t="s">
-        <v>162</v>
       </c>
       <c r="G101" s="8">
         <v>5</v>
@@ -10656,19 +10573,19 @@
         <v>99</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F102" s="8" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G102" s="8">
         <v>2</v>
@@ -10683,19 +10600,19 @@
         <v>100</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F103" s="8" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G103" s="8">
         <v>2</v>
@@ -10710,19 +10627,19 @@
         <v>101</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D104" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E104" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F104" s="8" t="s">
         <v>134</v>
-      </c>
-      <c r="E104" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="F104" s="8" t="s">
-        <v>136</v>
       </c>
       <c r="G104" s="8">
         <v>3</v>
@@ -10737,19 +10654,19 @@
         <v>102</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F105" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G105" s="8">
         <v>1</v>
@@ -10764,19 +10681,19 @@
         <v>103</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D106" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E106" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="F106" s="8" t="s">
         <v>134</v>
-      </c>
-      <c r="E106" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="F106" s="8" t="s">
-        <v>136</v>
       </c>
       <c r="G106" s="8">
         <v>3</v>
@@ -10791,19 +10708,19 @@
         <v>104</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F107" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G107" s="8">
         <v>1</v>
@@ -10818,19 +10735,19 @@
         <v>105</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F108" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G108" s="8">
         <v>3</v>
@@ -10845,19 +10762,19 @@
         <v>106</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F109" s="8" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="G109" s="8">
         <v>3</v>

--- a/周度_工厂配送兔司家门店货品对比表及销售排行表_格式化模板.xlsx
+++ b/周度_工厂配送兔司家门店货品对比表及销售排行表_格式化模板.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wadec\Documents\projects\mainyan-auto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEFD7F6F-2269-49E1-91AE-23F83F2421FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5A8FD6C-A0D6-4601-876A-13F782F6E819}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1536" yWindow="1536" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="配送门店业绩表 5.25-5.31" sheetId="4" r:id="rId1"/>
@@ -1230,6 +1230,9 @@
     <xf numFmtId="176" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1239,20 +1242,11 @@
     <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1266,20 +1260,26 @@
     <xf numFmtId="176" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1791,23 +1791,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="22" customFormat="1" ht="36" customHeight="1">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="38" t="s">
         <v>266</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="37"/>
-      <c r="M1" s="37"/>
-      <c r="N1" s="37"/>
-      <c r="O1" s="37"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+      <c r="N1" s="38"/>
+      <c r="O1" s="38"/>
       <c r="P1" s="21"/>
       <c r="Q1" s="21"/>
     </row>
@@ -1859,60 +1859,60 @@
       </c>
     </row>
     <row r="3" spans="1:17" ht="22.05" customHeight="1">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="52"/>
+      <c r="B3" s="42"/>
       <c r="C3" s="31">
-        <f>SUM(C4:C5)</f>
+        <f t="shared" ref="C3:H3" si="0">SUM(C4:C5)</f>
         <v>0</v>
       </c>
       <c r="D3" s="31">
-        <f>SUM(D4:D5)</f>
-        <v>0</v>
-      </c>
-      <c r="E3" s="32">
-        <f>SUM(E4:E5)</f>
-        <v>0</v>
-      </c>
-      <c r="F3" s="32">
-        <f>SUM(F4:F5)</f>
-        <v>0</v>
-      </c>
-      <c r="G3" s="32">
-        <f>SUM(G4:G5)</f>
-        <v>0</v>
-      </c>
-      <c r="H3" s="32">
-        <f>SUM(H4:H5)</f>
-        <v>0</v>
-      </c>
-      <c r="I3" s="33">
-        <f t="shared" ref="I3:O3" si="0">SUM(I4:I5)</f>
-        <v>0</v>
-      </c>
-      <c r="J3" s="33">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K3" s="33">
+      <c r="E3" s="32">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L3" s="33">
+      <c r="F3" s="32">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M3" s="33">
+      <c r="G3" s="32">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N3" s="33">
+      <c r="H3" s="32">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="I3" s="33">
+        <f t="shared" ref="I3:O3" si="1">SUM(I4:I5)</f>
+        <v>0</v>
+      </c>
+      <c r="J3" s="33">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K3" s="33">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L3" s="33">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M3" s="33">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N3" s="33">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="O3" s="33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -1929,8 +1929,11 @@
       </c>
       <c r="E4" s="32"/>
       <c r="F4" s="32"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="53"/>
+      <c r="G4" s="37">
+        <f>C4-F4-H4</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="37"/>
       <c r="I4" s="35"/>
       <c r="J4" s="35"/>
       <c r="K4" s="35"/>
@@ -1941,19 +1944,22 @@
     </row>
     <row r="5" spans="1:17" ht="22.05" customHeight="1">
       <c r="A5" s="28">
-        <f t="shared" ref="A5" si="1">ROW()-3</f>
+        <f t="shared" ref="A5" si="2">ROW()-3</f>
         <v>2</v>
       </c>
       <c r="B5" s="23"/>
       <c r="C5" s="34"/>
       <c r="D5" s="31">
-        <f t="shared" ref="D5" si="2">C5-F5</f>
+        <f t="shared" ref="D5" si="3">C5-F5</f>
         <v>0</v>
       </c>
       <c r="E5" s="32"/>
       <c r="F5" s="32"/>
-      <c r="G5" s="53"/>
-      <c r="H5" s="53"/>
+      <c r="G5" s="37">
+        <f>C5-F5-H5</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="37"/>
       <c r="I5" s="35"/>
       <c r="J5" s="35"/>
       <c r="K5" s="35"/>
@@ -2008,104 +2014,104 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" s="10" customFormat="1" ht="25.05" customHeight="1">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="46"/>
-      <c r="K1" s="45"/>
-      <c r="L1" s="46"/>
-      <c r="M1" s="45"/>
-      <c r="N1" s="46"/>
-      <c r="O1" s="45"/>
-      <c r="P1" s="46"/>
-      <c r="Q1" s="45"/>
-      <c r="R1" s="46"/>
-      <c r="S1" s="45"/>
-      <c r="T1" s="46"/>
-      <c r="U1" s="45"/>
-      <c r="V1" s="46"/>
-      <c r="W1" s="45"/>
-      <c r="X1" s="46"/>
-      <c r="Y1" s="45"/>
-      <c r="Z1" s="46"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="44"/>
+      <c r="K1" s="43"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="44"/>
+      <c r="Q1" s="43"/>
+      <c r="R1" s="44"/>
+      <c r="S1" s="43"/>
+      <c r="T1" s="44"/>
+      <c r="U1" s="43"/>
+      <c r="V1" s="44"/>
+      <c r="W1" s="43"/>
+      <c r="X1" s="44"/>
+      <c r="Y1" s="43"/>
+      <c r="Z1" s="44"/>
       <c r="AA1" s="11"/>
       <c r="AB1" s="12"/>
     </row>
     <row r="2" spans="1:28" ht="19.95" customHeight="1">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="43" t="s">
+      <c r="C2" s="52" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="43" t="s">
+      <c r="D2" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="43" t="s">
+      <c r="E2" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="43" t="s">
+      <c r="F2" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="47" t="s">
+      <c r="G2" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="48"/>
-      <c r="I2" s="42" t="s">
+      <c r="H2" s="46"/>
+      <c r="I2" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="49"/>
-      <c r="K2" s="42" t="s">
+      <c r="J2" s="48"/>
+      <c r="K2" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="L2" s="49"/>
-      <c r="M2" s="40" t="s">
+      <c r="L2" s="48"/>
+      <c r="M2" s="49" t="s">
         <v>18</v>
       </c>
       <c r="N2" s="50"/>
-      <c r="O2" s="40" t="s">
+      <c r="O2" s="49" t="s">
         <v>19</v>
       </c>
       <c r="P2" s="50"/>
-      <c r="Q2" s="40" t="s">
+      <c r="Q2" s="49" t="s">
         <v>20</v>
       </c>
       <c r="R2" s="50"/>
-      <c r="S2" s="40" t="s">
+      <c r="S2" s="49" t="s">
         <v>21</v>
       </c>
       <c r="T2" s="50"/>
-      <c r="U2" s="40" t="s">
+      <c r="U2" s="49" t="s">
         <v>22</v>
       </c>
       <c r="V2" s="50"/>
-      <c r="W2" s="40" t="s">
+      <c r="W2" s="49" t="s">
         <v>23</v>
       </c>
       <c r="X2" s="50"/>
-      <c r="Y2" s="42" t="s">
+      <c r="Y2" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="Z2" s="49"/>
+      <c r="Z2" s="48"/>
     </row>
     <row r="3" spans="1:28" ht="19.95" customHeight="1">
-      <c r="A3" s="41"/>
-      <c r="B3" s="42"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
+      <c r="A3" s="51"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
       <c r="G3" s="6" t="s">
         <v>25</v>
       </c>
@@ -2168,14 +2174,14 @@
       </c>
     </row>
     <row r="4" spans="1:28" ht="19.95" customHeight="1">
-      <c r="A4" s="40" t="s">
+      <c r="A4" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
+      <c r="B4" s="49"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
       <c r="G4" s="6">
         <f t="shared" ref="G4:L4" si="0">SUM(G5:G110)</f>
         <v>3063</v>
@@ -7825,6 +7831,13 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
     <mergeCell ref="A1:Z1"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="I2:J2"/>
@@ -7836,13 +7849,6 @@
     <mergeCell ref="U2:V2"/>
     <mergeCell ref="W2:X2"/>
     <mergeCell ref="Y2:Z2"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7866,16 +7872,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="43" t="s">
         <v>257</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="46"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="44"/>
     </row>
     <row r="2" spans="1:8" ht="19.95" customHeight="1">
       <c r="A2" s="4" t="s">
@@ -7904,14 +7910,14 @@
       </c>
     </row>
     <row r="3" spans="1:8" ht="19.95" customHeight="1">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
       <c r="G3" s="6">
         <f>SUM(G4:G109)</f>
         <v>3063</v>

--- a/周度_工厂配送兔司家门店货品对比表及销售排行表_格式化模板.xlsx
+++ b/周度_工厂配送兔司家门店货品对比表及销售排行表_格式化模板.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3824D5C-D214-4227-9C40-6BA71B92CD0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="配送门店业绩表 5.25-5.31" sheetId="4" r:id="rId1"/>
@@ -1220,6 +1220,75 @@
     <xf numFmtId="176" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1235,82 +1304,13 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1823,23 +1823,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="11" customFormat="1" ht="36" customHeight="1">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="50" t="s">
         <v>266</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="50"/>
+      <c r="M1" s="50"/>
+      <c r="N1" s="50"/>
+      <c r="O1" s="50"/>
       <c r="P1" s="10"/>
       <c r="Q1" s="10"/>
     </row>
@@ -1891,10 +1891,10 @@
       </c>
     </row>
     <row r="3" spans="1:17" ht="22.05" customHeight="1">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="31"/>
+      <c r="B3" s="54"/>
       <c r="C3" s="20">
         <f t="shared" ref="C3:H3" si="0">SUM(C4:C5)</f>
         <v>0</v>
@@ -2023,275 +2023,275 @@
     <col min="5" max="5" width="15.6640625" style="19" customWidth="1"/>
     <col min="6" max="6" width="4.21875" style="18" customWidth="1"/>
     <col min="7" max="7" width="6.77734375" style="18" customWidth="1"/>
-    <col min="8" max="8" width="10.33203125" style="56" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.33203125" style="37" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="4.6640625" style="18" customWidth="1"/>
-    <col min="10" max="10" width="8.6640625" style="56" customWidth="1"/>
+    <col min="10" max="10" width="8.6640625" style="37" customWidth="1"/>
     <col min="11" max="11" width="4.6640625" style="18" customWidth="1"/>
-    <col min="12" max="12" width="8.6640625" style="56" customWidth="1"/>
+    <col min="12" max="12" width="8.6640625" style="37" customWidth="1"/>
     <col min="13" max="13" width="4.6640625" style="18" customWidth="1"/>
-    <col min="14" max="14" width="8.6640625" style="56" customWidth="1"/>
+    <col min="14" max="14" width="8.6640625" style="37" customWidth="1"/>
     <col min="15" max="15" width="4.88671875" style="18" customWidth="1"/>
-    <col min="16" max="16" width="8.6640625" style="56" customWidth="1"/>
+    <col min="16" max="16" width="8.6640625" style="37" customWidth="1"/>
     <col min="17" max="17" width="4.6640625" style="18" customWidth="1"/>
-    <col min="18" max="18" width="8.6640625" style="56" customWidth="1"/>
+    <col min="18" max="18" width="8.6640625" style="37" customWidth="1"/>
     <col min="19" max="19" width="4.6640625" style="18" customWidth="1"/>
-    <col min="20" max="20" width="9.21875" style="56" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.21875" style="37" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="4.6640625" style="18" customWidth="1"/>
-    <col min="22" max="22" width="8.6640625" style="56" customWidth="1"/>
+    <col min="22" max="22" width="8.6640625" style="37" customWidth="1"/>
     <col min="23" max="23" width="4.6640625" style="18" customWidth="1"/>
-    <col min="24" max="24" width="9.21875" style="56" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.21875" style="37" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="4.6640625" style="18" customWidth="1"/>
-    <col min="26" max="26" width="9.21875" style="56" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.21875" style="37" bestFit="1" customWidth="1"/>
     <col min="27" max="16384" width="9" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" s="39" customFormat="1" ht="25.05" customHeight="1">
-      <c r="A1" s="35" t="s">
+    <row r="1" spans="1:28" s="29" customFormat="1" ht="25.05" customHeight="1">
+      <c r="A1" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="36"/>
-      <c r="K1" s="35"/>
-      <c r="L1" s="36"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="36"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="35"/>
-      <c r="R1" s="36"/>
-      <c r="S1" s="35"/>
-      <c r="T1" s="36"/>
-      <c r="U1" s="35"/>
-      <c r="V1" s="36"/>
-      <c r="W1" s="35"/>
-      <c r="X1" s="36"/>
-      <c r="Y1" s="35"/>
-      <c r="Z1" s="36"/>
-      <c r="AA1" s="37"/>
-      <c r="AB1" s="38"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="39"/>
+      <c r="L1" s="40"/>
+      <c r="M1" s="39"/>
+      <c r="N1" s="40"/>
+      <c r="O1" s="39"/>
+      <c r="P1" s="40"/>
+      <c r="Q1" s="39"/>
+      <c r="R1" s="40"/>
+      <c r="S1" s="39"/>
+      <c r="T1" s="40"/>
+      <c r="U1" s="39"/>
+      <c r="V1" s="40"/>
+      <c r="W1" s="39"/>
+      <c r="X1" s="40"/>
+      <c r="Y1" s="39"/>
+      <c r="Z1" s="40"/>
+      <c r="AA1" s="27"/>
+      <c r="AB1" s="28"/>
     </row>
     <row r="2" spans="1:28" ht="19.95" customHeight="1">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="42" t="s">
+      <c r="C2" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="42" t="s">
+      <c r="D2" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="42" t="s">
+      <c r="E2" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="42" t="s">
+      <c r="F2" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="43" t="s">
+      <c r="G2" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="44"/>
-      <c r="I2" s="41" t="s">
+      <c r="H2" s="42"/>
+      <c r="I2" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="45"/>
-      <c r="K2" s="41" t="s">
+      <c r="J2" s="44"/>
+      <c r="K2" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="L2" s="45"/>
-      <c r="M2" s="46" t="s">
+      <c r="L2" s="44"/>
+      <c r="M2" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="N2" s="47"/>
-      <c r="O2" s="46" t="s">
+      <c r="N2" s="46"/>
+      <c r="O2" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="46" t="s">
+      <c r="P2" s="46"/>
+      <c r="Q2" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="R2" s="47"/>
-      <c r="S2" s="46" t="s">
+      <c r="R2" s="46"/>
+      <c r="S2" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="T2" s="47"/>
-      <c r="U2" s="46" t="s">
+      <c r="T2" s="46"/>
+      <c r="U2" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="V2" s="47"/>
-      <c r="W2" s="46" t="s">
+      <c r="V2" s="46"/>
+      <c r="W2" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="X2" s="47"/>
-      <c r="Y2" s="41" t="s">
+      <c r="X2" s="46"/>
+      <c r="Y2" s="43" t="s">
         <v>24</v>
       </c>
-      <c r="Z2" s="45"/>
+      <c r="Z2" s="44"/>
     </row>
     <row r="3" spans="1:28" ht="19.95" customHeight="1">
-      <c r="A3" s="40"/>
-      <c r="B3" s="41"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="49" t="s">
+      <c r="A3" s="47"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="50" t="s">
+      <c r="H3" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="49" t="s">
+      <c r="I3" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="51" t="s">
+      <c r="J3" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="K3" s="49" t="s">
+      <c r="K3" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="L3" s="51" t="s">
+      <c r="L3" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="M3" s="52" t="s">
+      <c r="M3" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="N3" s="53" t="s">
+      <c r="N3" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="O3" s="52" t="s">
+      <c r="O3" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="P3" s="53" t="s">
+      <c r="P3" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="Q3" s="52" t="s">
+      <c r="Q3" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="R3" s="53" t="s">
+      <c r="R3" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="S3" s="52" t="s">
+      <c r="S3" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="T3" s="53" t="s">
+      <c r="T3" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="U3" s="52" t="s">
+      <c r="U3" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="V3" s="53" t="s">
+      <c r="V3" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="W3" s="52" t="s">
+      <c r="W3" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="X3" s="53" t="s">
+      <c r="X3" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="Y3" s="49" t="s">
+      <c r="Y3" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="Z3" s="51" t="s">
+      <c r="Z3" s="33" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:28" ht="19.95" customHeight="1">
-      <c r="A4" s="46" t="s">
+      <c r="A4" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="49">
-        <f>SUM(G5:G7)</f>
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="30">
+        <f t="shared" ref="G4:Z4" si="0">SUM(G5:G7)</f>
         <v>0</v>
       </c>
-      <c r="H4" s="50">
-        <f>SUM(H5:H7)</f>
+      <c r="H4" s="32">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I4" s="49">
-        <f>SUM(I5:I7)</f>
+      <c r="I4" s="30">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J4" s="51">
-        <f>SUM(J5:J7)</f>
+      <c r="J4" s="33">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K4" s="49">
-        <f>SUM(K5:K7)</f>
+      <c r="K4" s="30">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L4" s="51">
-        <f>SUM(L5:L7)</f>
+      <c r="L4" s="33">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M4" s="49">
-        <f>SUM(M5:M7)</f>
+      <c r="M4" s="30">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N4" s="51">
-        <f>SUM(N5:N7)</f>
+      <c r="N4" s="33">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O4" s="49">
-        <f>SUM(O5:O7)</f>
+      <c r="O4" s="30">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P4" s="51">
-        <f>SUM(P5:P7)</f>
+      <c r="P4" s="33">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q4" s="49">
-        <f>SUM(Q5:Q7)</f>
+      <c r="Q4" s="30">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R4" s="51">
-        <f>SUM(R5:R7)</f>
+      <c r="R4" s="33">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="S4" s="49">
-        <f>SUM(S5:S7)</f>
+      <c r="S4" s="30">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="T4" s="51">
-        <f>SUM(T5:T7)</f>
+      <c r="T4" s="33">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U4" s="49">
-        <f>SUM(U5:U7)</f>
+      <c r="U4" s="30">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V4" s="51">
-        <f>SUM(V5:V7)</f>
+      <c r="V4" s="33">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W4" s="49">
-        <f>SUM(W5:W7)</f>
+      <c r="W4" s="30">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="X4" s="51">
-        <f>SUM(X5:X7)</f>
+      <c r="X4" s="33">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Y4" s="49">
-        <f>SUM(Y5:Y7)</f>
+      <c r="Y4" s="30">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Z4" s="51">
-        <f>SUM(Z5:Z7)</f>
+      <c r="Z4" s="33">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2316,41 +2316,41 @@
         <v>31</v>
       </c>
       <c r="G5" s="17">
-        <f>SUM(I5,K5,M5,O5,Q5,S5,U5,W5,Y5)</f>
+        <f t="shared" ref="G5:H7" si="1">SUM(I5,K5,M5,O5,Q5,S5,U5,W5,Y5)</f>
         <v>0</v>
       </c>
-      <c r="H5" s="57">
-        <f>SUM(J5,L5,N5,P5,R5,T5,V5,X5,Z5)</f>
+      <c r="H5" s="38">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I5" s="17"/>
-      <c r="J5" s="54"/>
+      <c r="J5" s="35"/>
       <c r="K5" s="17"/>
-      <c r="L5" s="54"/>
+      <c r="L5" s="35"/>
       <c r="M5" s="17"/>
-      <c r="N5" s="54"/>
+      <c r="N5" s="35"/>
       <c r="O5" s="17"/>
-      <c r="P5" s="54"/>
+      <c r="P5" s="35"/>
       <c r="Q5" s="17"/>
-      <c r="R5" s="54"/>
+      <c r="R5" s="35"/>
       <c r="S5" s="17"/>
-      <c r="T5" s="54"/>
+      <c r="T5" s="35"/>
       <c r="U5" s="17"/>
-      <c r="V5" s="54"/>
+      <c r="V5" s="35"/>
       <c r="W5" s="17"/>
-      <c r="X5" s="54"/>
+      <c r="X5" s="35"/>
       <c r="Y5" s="17"/>
-      <c r="Z5" s="54"/>
+      <c r="Z5" s="35"/>
     </row>
     <row r="6" spans="1:28" ht="19.95" customHeight="1">
       <c r="A6" s="17">
-        <f t="shared" ref="A6" si="0">ROW()-4</f>
+        <f t="shared" ref="A6" si="2">ROW()-4</f>
         <v>2</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="55" t="s">
+      <c r="C6" s="36" t="s">
         <v>33</v>
       </c>
       <c r="D6" s="12" t="s">
@@ -2363,35 +2363,35 @@
         <v>35</v>
       </c>
       <c r="G6" s="17">
-        <f>SUM(I6,K6,M6,O6,Q6,S6,U6,W6,Y6)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H6" s="57">
-        <f>SUM(J6,L6,N6,P6,R6,T6,V6,X6,Z6)</f>
+      <c r="H6" s="38">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I6" s="17"/>
-      <c r="J6" s="54"/>
+      <c r="J6" s="35"/>
       <c r="K6" s="17"/>
-      <c r="L6" s="54"/>
+      <c r="L6" s="35"/>
       <c r="M6" s="17"/>
-      <c r="N6" s="54"/>
+      <c r="N6" s="35"/>
       <c r="O6" s="17"/>
-      <c r="P6" s="54"/>
+      <c r="P6" s="35"/>
       <c r="Q6" s="17"/>
-      <c r="R6" s="54"/>
+      <c r="R6" s="35"/>
       <c r="S6" s="17"/>
-      <c r="T6" s="54"/>
+      <c r="T6" s="35"/>
       <c r="U6" s="17"/>
-      <c r="V6" s="54"/>
+      <c r="V6" s="35"/>
       <c r="W6" s="17"/>
-      <c r="X6" s="54"/>
+      <c r="X6" s="35"/>
       <c r="Y6" s="17"/>
-      <c r="Z6" s="54"/>
+      <c r="Z6" s="35"/>
     </row>
     <row r="7" spans="1:28" ht="19.95" customHeight="1">
       <c r="A7" s="17">
-        <f t="shared" ref="A7" si="1">ROW()-4</f>
+        <f t="shared" ref="A7" si="3">ROW()-4</f>
         <v>3</v>
       </c>
       <c r="B7" s="12" t="s">
@@ -2410,34 +2410,41 @@
         <v>39</v>
       </c>
       <c r="G7" s="17">
-        <f>SUM(I7,K7,M7,O7,Q7,S7,U7,W7,Y7)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H7" s="57">
-        <f>SUM(J7,L7,N7,P7,R7,T7,V7,X7,Z7)</f>
+      <c r="H7" s="38">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I7" s="17"/>
-      <c r="J7" s="54"/>
+      <c r="J7" s="35"/>
       <c r="K7" s="17"/>
-      <c r="L7" s="54"/>
+      <c r="L7" s="35"/>
       <c r="M7" s="17"/>
-      <c r="N7" s="54"/>
+      <c r="N7" s="35"/>
       <c r="O7" s="17"/>
-      <c r="P7" s="54"/>
+      <c r="P7" s="35"/>
       <c r="Q7" s="17"/>
-      <c r="R7" s="54"/>
+      <c r="R7" s="35"/>
       <c r="S7" s="17"/>
-      <c r="T7" s="54"/>
+      <c r="T7" s="35"/>
       <c r="U7" s="17"/>
-      <c r="V7" s="54"/>
+      <c r="V7" s="35"/>
       <c r="W7" s="17"/>
-      <c r="X7" s="54"/>
+      <c r="X7" s="35"/>
       <c r="Y7" s="17"/>
-      <c r="Z7" s="54"/>
+      <c r="Z7" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
     <mergeCell ref="A1:Z1"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="I2:J2"/>
@@ -2449,13 +2456,6 @@
     <mergeCell ref="U2:V2"/>
     <mergeCell ref="W2:X2"/>
     <mergeCell ref="Y2:Z2"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2479,16 +2479,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="55" t="s">
         <v>257</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="34"/>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="56"/>
     </row>
     <row r="2" spans="1:8" ht="19.95" customHeight="1">
       <c r="A2" s="4" t="s">
@@ -2517,14 +2517,14 @@
       </c>
     </row>
     <row r="3" spans="1:8" ht="19.95" customHeight="1">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
       <c r="G3" s="6">
         <f>SUM(G4:G109)</f>
         <v>3063</v>

--- a/周度_工厂配送兔司家门店货品对比表及销售排行表_格式化模板.xlsx
+++ b/周度_工厂配送兔司家门店货品对比表及销售排行表_格式化模板.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wadec\Documents\projects\mainyan-auto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{879814B0-8DE5-4019-A2CB-1512B2F6707E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EA7D019-50CB-473F-A44F-F58AD712B8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="配送门店业绩表 5.25-5.31" sheetId="4" r:id="rId1"/>
@@ -463,9 +463,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -517,7 +514,16 @@
     <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -566,12 +572,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1069,8 +1069,9 @@
     <col min="2" max="2" width="18.21875" style="10" customWidth="1"/>
     <col min="3" max="3" width="12.21875" style="10" customWidth="1"/>
     <col min="4" max="4" width="12.109375" style="10" customWidth="1"/>
-    <col min="5" max="6" width="6.44140625" style="9" customWidth="1"/>
-    <col min="7" max="7" width="9.21875" style="10" customWidth="1"/>
+    <col min="5" max="5" width="6.44140625" style="9" customWidth="1"/>
+    <col min="6" max="6" width="9.21875" style="9" customWidth="1"/>
+    <col min="7" max="7" width="10.33203125" style="10" customWidth="1"/>
     <col min="8" max="8" width="10.33203125" style="10" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="9.109375" style="9" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="6.6640625" style="9" customWidth="1"/>
@@ -1084,23 +1085,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="2" customFormat="1" ht="36" customHeight="1">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
     </row>
@@ -1152,59 +1153,59 @@
       </c>
     </row>
     <row r="3" spans="1:17" ht="22.05" customHeight="1">
-      <c r="A3" s="33" t="s">
+      <c r="A3" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="11">
+      <c r="B3" s="36"/>
+      <c r="C3" s="13">
         <f t="shared" ref="C3:H3" si="0">SUM(C4:C5)</f>
         <v>0</v>
       </c>
-      <c r="D3" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E3" s="12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F3" s="12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G3" s="12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H3" s="12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I3" s="13">
+      <c r="D3" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E3" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F3" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G3" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H3" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I3" s="12">
         <f t="shared" ref="I3:O3" si="1">SUM(I4:I5)</f>
         <v>0</v>
       </c>
-      <c r="J3" s="13">
+      <c r="J3" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K3" s="13">
+      <c r="K3" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L3" s="13">
+      <c r="L3" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M3" s="13">
+      <c r="M3" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N3" s="13">
+      <c r="N3" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O3" s="13">
+      <c r="O3" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1215,24 +1216,24 @@
         <v>1</v>
       </c>
       <c r="B4" s="3"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="11">
+      <c r="C4" s="13"/>
+      <c r="D4" s="13">
         <f>C4-F4</f>
         <v>0</v>
       </c>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="17">
+      <c r="E4" s="11"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16">
         <f>C4-F4-H4</f>
         <v>0</v>
       </c>
-      <c r="H4" s="17"/>
-      <c r="I4" s="15"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="15"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="16"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
+      <c r="N4" s="15"/>
       <c r="O4" s="15"/>
     </row>
     <row r="5" spans="1:17" ht="22.05" customHeight="1">
@@ -1241,24 +1242,24 @@
         <v>2</v>
       </c>
       <c r="B5" s="3"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="11">
+      <c r="C5" s="13"/>
+      <c r="D5" s="13">
         <f t="shared" ref="D5" si="3">C5-F5</f>
         <v>0</v>
       </c>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="17">
+      <c r="E5" s="11"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16">
         <f>C5-F5-H5</f>
         <v>0</v>
       </c>
-      <c r="H5" s="17"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="15"/>
-      <c r="K5" s="15"/>
-      <c r="L5" s="15"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="16"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14"/>
+      <c r="L5" s="14"/>
+      <c r="M5" s="14"/>
+      <c r="N5" s="15"/>
       <c r="O5" s="15"/>
     </row>
   </sheetData>
@@ -1284,274 +1285,274 @@
     <col min="5" max="5" width="15.6640625" style="10" customWidth="1"/>
     <col min="6" max="6" width="4.21875" style="9" customWidth="1"/>
     <col min="7" max="7" width="6.77734375" style="9" customWidth="1"/>
-    <col min="8" max="8" width="10.33203125" style="28" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.33203125" style="27" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="4.6640625" style="9" customWidth="1"/>
-    <col min="10" max="10" width="8.6640625" style="28" customWidth="1"/>
+    <col min="10" max="10" width="8.6640625" style="27" customWidth="1"/>
     <col min="11" max="11" width="4.6640625" style="9" customWidth="1"/>
-    <col min="12" max="12" width="8.6640625" style="28" customWidth="1"/>
+    <col min="12" max="12" width="8.6640625" style="27" customWidth="1"/>
     <col min="13" max="13" width="4.6640625" style="9" customWidth="1"/>
-    <col min="14" max="14" width="8.6640625" style="28" customWidth="1"/>
+    <col min="14" max="14" width="8.6640625" style="27" customWidth="1"/>
     <col min="15" max="15" width="4.88671875" style="9" customWidth="1"/>
-    <col min="16" max="16" width="8.6640625" style="28" customWidth="1"/>
+    <col min="16" max="16" width="8.6640625" style="27" customWidth="1"/>
     <col min="17" max="17" width="4.6640625" style="9" customWidth="1"/>
-    <col min="18" max="18" width="8.6640625" style="28" customWidth="1"/>
+    <col min="18" max="18" width="8.6640625" style="27" customWidth="1"/>
     <col min="19" max="19" width="4.6640625" style="9" customWidth="1"/>
-    <col min="20" max="20" width="9.21875" style="28" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.21875" style="27" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="4.6640625" style="9" customWidth="1"/>
-    <col min="22" max="22" width="8.6640625" style="28" customWidth="1"/>
+    <col min="22" max="22" width="8.6640625" style="27" customWidth="1"/>
     <col min="23" max="23" width="4.6640625" style="9" customWidth="1"/>
-    <col min="24" max="24" width="9.21875" style="28" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.21875" style="27" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="4.6640625" style="9" customWidth="1"/>
-    <col min="26" max="26" width="9.21875" style="28" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.21875" style="27" bestFit="1" customWidth="1"/>
     <col min="27" max="16384" width="9" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" s="20" customFormat="1" ht="25.05" customHeight="1">
-      <c r="A1" s="40" t="s">
+    <row r="1" spans="1:28" s="19" customFormat="1" ht="25.05" customHeight="1">
+      <c r="A1" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="40"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="40"/>
-      <c r="P1" s="41"/>
-      <c r="Q1" s="40"/>
-      <c r="R1" s="41"/>
-      <c r="S1" s="40"/>
-      <c r="T1" s="41"/>
-      <c r="U1" s="40"/>
-      <c r="V1" s="41"/>
-      <c r="W1" s="40"/>
-      <c r="X1" s="41"/>
-      <c r="Y1" s="40"/>
-      <c r="Z1" s="41"/>
-      <c r="AA1" s="18"/>
-      <c r="AB1" s="19"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="42"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="42"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="42"/>
+      <c r="P1" s="43"/>
+      <c r="Q1" s="42"/>
+      <c r="R1" s="43"/>
+      <c r="S1" s="42"/>
+      <c r="T1" s="43"/>
+      <c r="U1" s="42"/>
+      <c r="V1" s="43"/>
+      <c r="W1" s="42"/>
+      <c r="X1" s="43"/>
+      <c r="Y1" s="42"/>
+      <c r="Z1" s="43"/>
+      <c r="AA1" s="17"/>
+      <c r="AB1" s="18"/>
     </row>
     <row r="2" spans="1:28" ht="19.95" customHeight="1">
-      <c r="A2" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="37" t="s">
+      <c r="A2" s="38" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="38" t="s">
+      <c r="C2" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="38" t="s">
+      <c r="D2" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="38" t="s">
+      <c r="E2" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="38" t="s">
+      <c r="F2" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="42" t="s">
+      <c r="G2" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="43"/>
-      <c r="I2" s="37" t="s">
+      <c r="H2" s="45"/>
+      <c r="I2" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="44"/>
-      <c r="K2" s="37" t="s">
+      <c r="J2" s="46"/>
+      <c r="K2" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="L2" s="44"/>
-      <c r="M2" s="35" t="s">
+      <c r="L2" s="46"/>
+      <c r="M2" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="N2" s="45"/>
-      <c r="O2" s="35" t="s">
+      <c r="N2" s="47"/>
+      <c r="O2" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="P2" s="45"/>
-      <c r="Q2" s="35" t="s">
+      <c r="P2" s="47"/>
+      <c r="Q2" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="R2" s="45"/>
-      <c r="S2" s="35" t="s">
+      <c r="R2" s="47"/>
+      <c r="S2" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="T2" s="45"/>
-      <c r="U2" s="35" t="s">
+      <c r="T2" s="47"/>
+      <c r="U2" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="V2" s="45"/>
-      <c r="W2" s="35" t="s">
+      <c r="V2" s="47"/>
+      <c r="W2" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="X2" s="45"/>
-      <c r="Y2" s="37" t="s">
+      <c r="X2" s="47"/>
+      <c r="Y2" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="Z2" s="44"/>
+      <c r="Z2" s="46"/>
     </row>
     <row r="3" spans="1:28" ht="19.95" customHeight="1">
-      <c r="A3" s="36"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="21" t="s">
+      <c r="A3" s="38"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="23" t="s">
+      <c r="H3" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="21" t="s">
+      <c r="I3" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="24" t="s">
+      <c r="J3" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="K3" s="21" t="s">
+      <c r="K3" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="L3" s="24" t="s">
+      <c r="L3" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="M3" s="22" t="s">
+      <c r="M3" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="N3" s="25" t="s">
+      <c r="N3" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="O3" s="22" t="s">
+      <c r="O3" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="P3" s="25" t="s">
+      <c r="P3" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="Q3" s="22" t="s">
+      <c r="Q3" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="R3" s="25" t="s">
+      <c r="R3" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="S3" s="22" t="s">
+      <c r="S3" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="T3" s="25" t="s">
+      <c r="T3" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="U3" s="22" t="s">
+      <c r="U3" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="V3" s="25" t="s">
+      <c r="V3" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="W3" s="22" t="s">
+      <c r="W3" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="X3" s="25" t="s">
+      <c r="X3" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="Y3" s="21" t="s">
+      <c r="Y3" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="Z3" s="24" t="s">
+      <c r="Z3" s="23" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:28" ht="19.95" customHeight="1">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="35"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="21">
+      <c r="B4" s="37"/>
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="20">
         <f t="shared" ref="G4:Z4" si="0">SUM(G5:G7)</f>
         <v>0</v>
       </c>
-      <c r="H4" s="23">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I4" s="21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J4" s="24">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K4" s="21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L4" s="24">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M4" s="21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N4" s="24">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O4" s="21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="P4" s="24">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Q4" s="21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R4" s="24">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S4" s="21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="T4" s="24">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U4" s="21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="V4" s="24">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W4" s="21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X4" s="24">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y4" s="21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Z4" s="24">
+      <c r="H4" s="22">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I4" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J4" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K4" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L4" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M4" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N4" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O4" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P4" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q4" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R4" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S4" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="T4" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U4" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="V4" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W4" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X4" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Y4" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Z4" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -1570,28 +1571,28 @@
         <f t="shared" ref="G5:H7" si="1">SUM(I5,K5,M5,O5,Q5,S5,U5,W5,Y5)</f>
         <v>0</v>
       </c>
-      <c r="H5" s="29">
+      <c r="H5" s="31">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I5" s="8"/>
-      <c r="J5" s="26"/>
+      <c r="J5" s="25"/>
       <c r="K5" s="8"/>
-      <c r="L5" s="26"/>
+      <c r="L5" s="25"/>
       <c r="M5" s="8"/>
-      <c r="N5" s="26"/>
+      <c r="N5" s="25"/>
       <c r="O5" s="8"/>
-      <c r="P5" s="26"/>
+      <c r="P5" s="25"/>
       <c r="Q5" s="8"/>
-      <c r="R5" s="26"/>
+      <c r="R5" s="25"/>
       <c r="S5" s="8"/>
-      <c r="T5" s="26"/>
+      <c r="T5" s="25"/>
       <c r="U5" s="8"/>
-      <c r="V5" s="26"/>
+      <c r="V5" s="25"/>
       <c r="W5" s="8"/>
-      <c r="X5" s="26"/>
+      <c r="X5" s="25"/>
       <c r="Y5" s="8"/>
-      <c r="Z5" s="26"/>
+      <c r="Z5" s="25"/>
     </row>
     <row r="6" spans="1:28" ht="19.95" customHeight="1">
       <c r="A6" s="8">
@@ -1599,7 +1600,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="3"/>
-      <c r="C6" s="27"/>
+      <c r="C6" s="26"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="8"/>
@@ -1607,28 +1608,28 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H6" s="29">
+      <c r="H6" s="31">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I6" s="8"/>
-      <c r="J6" s="26"/>
+      <c r="J6" s="25"/>
       <c r="K6" s="8"/>
-      <c r="L6" s="26"/>
+      <c r="L6" s="25"/>
       <c r="M6" s="8"/>
-      <c r="N6" s="26"/>
+      <c r="N6" s="25"/>
       <c r="O6" s="8"/>
-      <c r="P6" s="26"/>
+      <c r="P6" s="25"/>
       <c r="Q6" s="8"/>
-      <c r="R6" s="26"/>
+      <c r="R6" s="25"/>
       <c r="S6" s="8"/>
-      <c r="T6" s="26"/>
+      <c r="T6" s="25"/>
       <c r="U6" s="8"/>
-      <c r="V6" s="26"/>
+      <c r="V6" s="25"/>
       <c r="W6" s="8"/>
-      <c r="X6" s="26"/>
+      <c r="X6" s="25"/>
       <c r="Y6" s="8"/>
-      <c r="Z6" s="26"/>
+      <c r="Z6" s="25"/>
     </row>
     <row r="7" spans="1:28" ht="19.95" customHeight="1">
       <c r="A7" s="8">
@@ -1644,28 +1645,28 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H7" s="29">
+      <c r="H7" s="31">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I7" s="8"/>
-      <c r="J7" s="26"/>
+      <c r="J7" s="25"/>
       <c r="K7" s="8"/>
-      <c r="L7" s="26"/>
+      <c r="L7" s="25"/>
       <c r="M7" s="8"/>
-      <c r="N7" s="26"/>
+      <c r="N7" s="25"/>
       <c r="O7" s="8"/>
-      <c r="P7" s="26"/>
+      <c r="P7" s="25"/>
       <c r="Q7" s="8"/>
-      <c r="R7" s="26"/>
+      <c r="R7" s="25"/>
       <c r="S7" s="8"/>
-      <c r="T7" s="26"/>
+      <c r="T7" s="25"/>
       <c r="U7" s="8"/>
-      <c r="V7" s="26"/>
+      <c r="V7" s="25"/>
       <c r="W7" s="8"/>
-      <c r="X7" s="26"/>
+      <c r="X7" s="25"/>
       <c r="Y7" s="8"/>
-      <c r="Z7" s="26"/>
+      <c r="Z7" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -1705,62 +1706,62 @@
     <col min="5" max="5" width="15.6640625" style="10" customWidth="1"/>
     <col min="6" max="6" width="4.21875" style="9" customWidth="1"/>
     <col min="7" max="7" width="8.6640625" style="9" customWidth="1"/>
-    <col min="8" max="8" width="10.109375" style="28" customWidth="1"/>
+    <col min="8" max="8" width="10.109375" style="27" customWidth="1"/>
     <col min="9" max="16384" width="9" style="10"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="41"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="43"/>
     </row>
     <row r="2" spans="1:8" ht="19.95" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="46" t="s">
+      <c r="C2" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="46" t="s">
+      <c r="D2" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="46" t="s">
+      <c r="E2" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="G2" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="H2" s="23" t="s">
+      <c r="H2" s="22" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="19.95" customHeight="1">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="35"/>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="21">
+      <c r="B3" s="37"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="20">
         <f>SUM(G4:G6)</f>
         <v>0</v>
       </c>
-      <c r="H3" s="23">
+      <c r="H3" s="22">
         <f>SUM(H4:H6)</f>
         <v>0</v>
       </c>
@@ -1776,7 +1777,7 @@
       <c r="E4" s="3"/>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
-      <c r="H4" s="47"/>
+      <c r="H4" s="29"/>
     </row>
     <row r="5" spans="1:8" ht="19.95" customHeight="1">
       <c r="A5" s="8">
@@ -1789,7 +1790,7 @@
       <c r="E5" s="3"/>
       <c r="F5" s="8"/>
       <c r="G5" s="8"/>
-      <c r="H5" s="47"/>
+      <c r="H5" s="29"/>
     </row>
     <row r="6" spans="1:8" ht="19.95" customHeight="1">
       <c r="A6" s="8">
@@ -1802,7 +1803,7 @@
       <c r="E6" s="3"/>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
-      <c r="H6" s="47"/>
+      <c r="H6" s="29"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:H7">
